--- a/data/papaya_phenotypes_2024_2025.xlsx
+++ b/data/papaya_phenotypes_2024_2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danie\Desktop\Capítulo 3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d23904a132a03eb6/GitHub/Bayesian-ridge-regression-papaya/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FD01266-7C60-4AB6-8242-19AA88424BB1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="60" documentId="13_ncr:1_{9FD01266-7C60-4AB6-8242-19AA88424BB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31941C01-8A8D-4DB6-98A0-EA7C6609EE24}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20736" windowHeight="11160" activeTab="2" xr2:uid="{A5324A72-5672-4083-BB8D-46249536C53E}"/>
+    <workbookView xWindow="-23148" yWindow="3708" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{A5324A72-5672-4083-BB8D-46249536C53E}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadados" sheetId="4" r:id="rId1"/>
@@ -21,6 +21,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -172,7 +183,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -242,7 +253,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -253,19 +264,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -283,7 +294,7 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -292,7 +303,7 @@
     <xf numFmtId="2" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -301,7 +312,7 @@
     <xf numFmtId="2" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -322,22 +333,22 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -346,7 +357,7 @@
     <xf numFmtId="2" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -355,11 +366,10 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1832,10 +1842,14 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office 2013 - 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1873,7 +1887,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1979,7 +1993,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2121,7 +2135,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2130,7 +2144,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FED3448-F94E-4AFA-98AA-57B3D8E8E122}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <drawing r:id="rId1"/>
@@ -2140,36 +2154,36 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B86CB596-1DA6-4665-AFC6-0635E255A783}">
   <dimension ref="A1:BD601"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" style="2" hidden="1" customWidth="1"/>
-    <col min="2" max="3" width="9.109375" style="2"/>
-    <col min="4" max="4" width="12.44140625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="9.109375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="13.6640625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="14.6640625" style="28" customWidth="1"/>
-    <col min="8" max="8" width="17.6640625" style="28" customWidth="1"/>
-    <col min="9" max="9" width="12.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.88671875" style="28" customWidth="1"/>
-    <col min="11" max="11" width="19.88671875" style="29" customWidth="1"/>
-    <col min="12" max="12" width="20.88671875" style="30" customWidth="1"/>
-    <col min="13" max="13" width="10.77734375" style="29" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="20.44140625" style="27" customWidth="1"/>
-    <col min="15" max="15" width="19.44140625" style="2" customWidth="1"/>
-    <col min="16" max="16" width="20.44140625" style="27" customWidth="1"/>
-    <col min="17" max="17" width="10.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="20.33203125" style="28" customWidth="1"/>
-    <col min="19" max="19" width="19.33203125" style="31" customWidth="1"/>
-    <col min="20" max="20" width="20.33203125" style="32" customWidth="1"/>
+    <col min="1" max="1" width="10.90625" style="2" hidden="1" customWidth="1"/>
+    <col min="2" max="3" width="9.08984375" style="2"/>
+    <col min="4" max="4" width="12.453125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="9.08984375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="13.6328125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="14.6328125" style="28" customWidth="1"/>
+    <col min="8" max="8" width="17.6328125" style="28" customWidth="1"/>
+    <col min="9" max="9" width="12.08984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.90625" style="28" customWidth="1"/>
+    <col min="11" max="11" width="19.90625" style="29" customWidth="1"/>
+    <col min="12" max="12" width="20.90625" style="30" customWidth="1"/>
+    <col min="13" max="13" width="10.81640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20.453125" style="27" customWidth="1"/>
+    <col min="15" max="15" width="19.453125" style="2" customWidth="1"/>
+    <col min="16" max="16" width="20.453125" style="27" customWidth="1"/>
+    <col min="17" max="17" width="10.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="20.36328125" style="28" customWidth="1"/>
+    <col min="19" max="19" width="19.36328125" style="31" customWidth="1"/>
+    <col min="20" max="20" width="20.36328125" style="32" customWidth="1"/>
     <col min="21" max="21" width="11" style="31" bestFit="1" customWidth="1"/>
-    <col min="22" max="34" width="9.109375" style="2" customWidth="1"/>
-    <col min="35" max="52" width="9.109375" style="2"/>
-    <col min="53" max="53" width="15.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="54" max="55" width="9.88671875" style="2" customWidth="1"/>
-    <col min="56" max="16384" width="9.109375" style="2"/>
+    <col min="22" max="34" width="9.08984375" style="2" customWidth="1"/>
+    <col min="35" max="52" width="9.08984375" style="2"/>
+    <col min="53" max="53" width="15.90625" style="2" bestFit="1" customWidth="1"/>
+    <col min="54" max="55" width="9.90625" style="2" customWidth="1"/>
+    <col min="56" max="16384" width="9.08984375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>9</v>
       </c>
@@ -2280,7 +2294,7 @@
       </c>
       <c r="BB1" s="12"/>
     </row>
-    <row r="2" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -2400,7 +2414,7 @@
       </c>
       <c r="AK2"/>
     </row>
-    <row r="3" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -2520,7 +2534,7 @@
       </c>
       <c r="AK3"/>
     </row>
-    <row r="4" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -2639,7 +2653,7 @@
       </c>
       <c r="AK4"/>
     </row>
-    <row r="5" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -2758,7 +2772,7 @@
       </c>
       <c r="AK5"/>
     </row>
-    <row r="6" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -2877,7 +2891,7 @@
       </c>
       <c r="AK6"/>
     </row>
-    <row r="7" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -2996,7 +3010,7 @@
       </c>
       <c r="AK7"/>
     </row>
-    <row r="8" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -3115,7 +3129,7 @@
       </c>
       <c r="AK8"/>
     </row>
-    <row r="9" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -3234,7 +3248,7 @@
       </c>
       <c r="AK9"/>
     </row>
-    <row r="10" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -3353,7 +3367,7 @@
       </c>
       <c r="AK10"/>
     </row>
-    <row r="11" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -3472,7 +3486,7 @@
       </c>
       <c r="AK11"/>
     </row>
-    <row r="12" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -3591,7 +3605,7 @@
       </c>
       <c r="AK12"/>
     </row>
-    <row r="13" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -3710,7 +3724,7 @@
       </c>
       <c r="AK13"/>
     </row>
-    <row r="14" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -3829,7 +3843,7 @@
       </c>
       <c r="AK14"/>
     </row>
-    <row r="15" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -3948,7 +3962,7 @@
       </c>
       <c r="AK15"/>
     </row>
-    <row r="16" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -4067,7 +4081,7 @@
       </c>
       <c r="AK16"/>
     </row>
-    <row r="17" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>19</v>
       </c>
@@ -4187,7 +4201,7 @@
       <c r="AK17"/>
       <c r="AL17"/>
     </row>
-    <row r="18" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>20</v>
       </c>
@@ -4307,7 +4321,7 @@
       <c r="AK18"/>
       <c r="AL18"/>
     </row>
-    <row r="19" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>21</v>
       </c>
@@ -4426,7 +4440,7 @@
       </c>
       <c r="AK19"/>
     </row>
-    <row r="20" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>22</v>
       </c>
@@ -4545,7 +4559,7 @@
       </c>
       <c r="AK20"/>
     </row>
-    <row r="21" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <v>23</v>
       </c>
@@ -4663,7 +4677,7 @@
         <v>81.069999999999993</v>
       </c>
     </row>
-    <row r="22" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>24</v>
       </c>
@@ -4781,7 +4795,7 @@
         <v>65.25</v>
       </c>
     </row>
-    <row r="23" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A23" s="3">
         <v>25</v>
       </c>
@@ -4899,7 +4913,7 @@
         <v>95.17</v>
       </c>
     </row>
-    <row r="24" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A24" s="3">
         <v>26</v>
       </c>
@@ -5017,7 +5031,7 @@
         <v>101.38</v>
       </c>
     </row>
-    <row r="25" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A25" s="3">
         <v>27</v>
       </c>
@@ -5135,7 +5149,7 @@
         <v>87.02</v>
       </c>
     </row>
-    <row r="26" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A26" s="3">
         <v>28</v>
       </c>
@@ -5253,7 +5267,7 @@
         <v>91.47</v>
       </c>
     </row>
-    <row r="27" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A27" s="3">
         <v>29</v>
       </c>
@@ -5371,7 +5385,7 @@
         <v>69.680000000000007</v>
       </c>
     </row>
-    <row r="28" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A28" s="3">
         <v>30</v>
       </c>
@@ -5489,7 +5503,7 @@
         <v>71.95</v>
       </c>
     </row>
-    <row r="29" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A29" s="3">
         <v>31</v>
       </c>
@@ -5607,7 +5621,7 @@
         <v>78.47</v>
       </c>
     </row>
-    <row r="30" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A30" s="3">
         <v>32</v>
       </c>
@@ -5725,7 +5739,7 @@
         <v>72.33</v>
       </c>
     </row>
-    <row r="31" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A31" s="3">
         <v>33</v>
       </c>
@@ -5843,7 +5857,7 @@
         <v>68.959999999999994</v>
       </c>
     </row>
-    <row r="32" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A32" s="3">
         <v>37</v>
       </c>
@@ -5961,7 +5975,7 @@
         <v>88.21</v>
       </c>
     </row>
-    <row r="33" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A33" s="3">
         <v>38</v>
       </c>
@@ -6079,7 +6093,7 @@
         <v>77.010000000000005</v>
       </c>
     </row>
-    <row r="34" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A34" s="3">
         <v>39</v>
       </c>
@@ -6197,7 +6211,7 @@
         <v>88.01</v>
       </c>
     </row>
-    <row r="35" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A35" s="3">
         <v>40</v>
       </c>
@@ -6315,7 +6329,7 @@
         <v>77.8</v>
       </c>
     </row>
-    <row r="36" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A36" s="3">
         <v>41</v>
       </c>
@@ -6433,7 +6447,7 @@
         <v>83.85</v>
       </c>
     </row>
-    <row r="37" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A37" s="3">
         <v>42</v>
       </c>
@@ -6551,7 +6565,7 @@
         <v>78.81</v>
       </c>
     </row>
-    <row r="38" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A38" s="3">
         <v>43</v>
       </c>
@@ -6670,7 +6684,7 @@
       </c>
       <c r="BB38" s="12"/>
     </row>
-    <row r="39" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A39" s="3">
         <v>44</v>
       </c>
@@ -6789,7 +6803,7 @@
       </c>
       <c r="BB39" s="12"/>
     </row>
-    <row r="40" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A40" s="3">
         <v>45</v>
       </c>
@@ -6908,7 +6922,7 @@
       </c>
       <c r="BB40" s="12"/>
     </row>
-    <row r="41" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A41" s="3">
         <v>46</v>
       </c>
@@ -7027,7 +7041,7 @@
       </c>
       <c r="BB41" s="12"/>
     </row>
-    <row r="42" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A42" s="3">
         <v>47</v>
       </c>
@@ -7146,7 +7160,7 @@
       </c>
       <c r="BB42" s="12"/>
     </row>
-    <row r="43" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A43" s="3">
         <v>48</v>
       </c>
@@ -7265,7 +7279,7 @@
       </c>
       <c r="BB43" s="12"/>
     </row>
-    <row r="44" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A44" s="3">
         <v>49</v>
       </c>
@@ -7384,7 +7398,7 @@
       </c>
       <c r="BB44" s="12"/>
     </row>
-    <row r="45" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A45" s="3">
         <v>50</v>
       </c>
@@ -7503,7 +7517,7 @@
       </c>
       <c r="BB45" s="12"/>
     </row>
-    <row r="46" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A46" s="3">
         <v>51</v>
       </c>
@@ -7622,7 +7636,7 @@
       </c>
       <c r="BB46" s="12"/>
     </row>
-    <row r="47" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A47" s="3">
         <v>55</v>
       </c>
@@ -7741,7 +7755,7 @@
       </c>
       <c r="BB47" s="12"/>
     </row>
-    <row r="48" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A48" s="3">
         <v>56</v>
       </c>
@@ -7860,7 +7874,7 @@
       </c>
       <c r="BB48" s="12"/>
     </row>
-    <row r="49" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A49" s="3">
         <v>57</v>
       </c>
@@ -7979,7 +7993,7 @@
       </c>
       <c r="BB49" s="12"/>
     </row>
-    <row r="50" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A50" s="3">
         <v>58</v>
       </c>
@@ -8098,7 +8112,7 @@
       </c>
       <c r="BB50" s="12"/>
     </row>
-    <row r="51" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A51" s="3">
         <v>59</v>
       </c>
@@ -8217,7 +8231,7 @@
       </c>
       <c r="BB51" s="12"/>
     </row>
-    <row r="52" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A52" s="3">
         <v>60</v>
       </c>
@@ -8336,7 +8350,7 @@
       </c>
       <c r="BB52" s="12"/>
     </row>
-    <row r="53" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A53" s="3">
         <v>61</v>
       </c>
@@ -8455,7 +8469,7 @@
       </c>
       <c r="BB53" s="12"/>
     </row>
-    <row r="54" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A54" s="3">
         <v>62</v>
       </c>
@@ -8574,7 +8588,7 @@
       </c>
       <c r="BB54" s="12"/>
     </row>
-    <row r="55" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A55" s="3">
         <v>63</v>
       </c>
@@ -8693,7 +8707,7 @@
       </c>
       <c r="BB55" s="12"/>
     </row>
-    <row r="56" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A56" s="3">
         <v>64</v>
       </c>
@@ -8812,7 +8826,7 @@
       </c>
       <c r="BB56" s="12"/>
     </row>
-    <row r="57" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A57" s="3">
         <v>65</v>
       </c>
@@ -8933,7 +8947,7 @@
       <c r="BC57" s="23"/>
       <c r="BD57" s="23"/>
     </row>
-    <row r="58" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A58" s="3">
         <v>66</v>
       </c>
@@ -9052,7 +9066,7 @@
       </c>
       <c r="BB58" s="12"/>
     </row>
-    <row r="59" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A59" s="3">
         <v>67</v>
       </c>
@@ -9171,7 +9185,7 @@
       </c>
       <c r="BB59" s="12"/>
     </row>
-    <row r="60" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A60" s="3">
         <v>68</v>
       </c>
@@ -9290,7 +9304,7 @@
       </c>
       <c r="BB60" s="12"/>
     </row>
-    <row r="61" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A61" s="3">
         <v>69</v>
       </c>
@@ -9409,7 +9423,7 @@
       </c>
       <c r="BB61" s="12"/>
     </row>
-    <row r="62" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A62" s="3">
         <v>73</v>
       </c>
@@ -9527,7 +9541,7 @@
         <v>74.069999999999993</v>
       </c>
     </row>
-    <row r="63" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A63" s="3">
         <v>74</v>
       </c>
@@ -9646,7 +9660,7 @@
       </c>
       <c r="BB63" s="12"/>
     </row>
-    <row r="64" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A64" s="3">
         <v>75</v>
       </c>
@@ -9765,7 +9779,7 @@
       </c>
       <c r="BB64" s="12"/>
     </row>
-    <row r="65" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A65" s="3">
         <v>76</v>
       </c>
@@ -9884,7 +9898,7 @@
       </c>
       <c r="BB65" s="12"/>
     </row>
-    <row r="66" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A66" s="3">
         <v>77</v>
       </c>
@@ -10003,7 +10017,7 @@
       </c>
       <c r="BB66" s="12"/>
     </row>
-    <row r="67" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A67" s="3">
         <v>78</v>
       </c>
@@ -10122,7 +10136,7 @@
       </c>
       <c r="BB67" s="12"/>
     </row>
-    <row r="68" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A68" s="3">
         <v>79</v>
       </c>
@@ -10241,7 +10255,7 @@
       </c>
       <c r="BB68" s="12"/>
     </row>
-    <row r="69" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A69" s="3">
         <v>80</v>
       </c>
@@ -10360,7 +10374,7 @@
       </c>
       <c r="BB69" s="12"/>
     </row>
-    <row r="70" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A70" s="3">
         <v>81</v>
       </c>
@@ -10479,7 +10493,7 @@
       </c>
       <c r="BB70" s="12"/>
     </row>
-    <row r="71" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A71" s="3">
         <v>82</v>
       </c>
@@ -10598,7 +10612,7 @@
       </c>
       <c r="BB71" s="12"/>
     </row>
-    <row r="72" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A72" s="3">
         <v>83</v>
       </c>
@@ -10717,7 +10731,7 @@
       </c>
       <c r="BB72" s="12"/>
     </row>
-    <row r="73" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A73" s="3">
         <v>84</v>
       </c>
@@ -10836,7 +10850,7 @@
       </c>
       <c r="BB73" s="12"/>
     </row>
-    <row r="74" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A74" s="3">
         <v>85</v>
       </c>
@@ -10955,7 +10969,7 @@
       </c>
       <c r="BB74" s="12"/>
     </row>
-    <row r="75" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A75" s="3">
         <v>86</v>
       </c>
@@ -11074,7 +11088,7 @@
       </c>
       <c r="BB75" s="12"/>
     </row>
-    <row r="76" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A76" s="3">
         <v>87</v>
       </c>
@@ -11193,7 +11207,7 @@
       </c>
       <c r="BB76" s="12"/>
     </row>
-    <row r="77" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A77" s="3">
         <v>88</v>
       </c>
@@ -11312,7 +11326,7 @@
       </c>
       <c r="BB77" s="12"/>
     </row>
-    <row r="78" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A78" s="3">
         <v>89</v>
       </c>
@@ -11431,7 +11445,7 @@
       </c>
       <c r="BB78" s="12"/>
     </row>
-    <row r="79" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A79" s="3">
         <v>90</v>
       </c>
@@ -11550,7 +11564,7 @@
       </c>
       <c r="BB79" s="12"/>
     </row>
-    <row r="80" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A80" s="3">
         <v>91</v>
       </c>
@@ -11669,7 +11683,7 @@
       </c>
       <c r="BB80" s="12"/>
     </row>
-    <row r="81" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A81" s="3">
         <v>92</v>
       </c>
@@ -11788,7 +11802,7 @@
       </c>
       <c r="BB81" s="12"/>
     </row>
-    <row r="82" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A82" s="3">
         <v>93</v>
       </c>
@@ -11907,7 +11921,7 @@
       </c>
       <c r="BB82" s="12"/>
     </row>
-    <row r="83" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A83" s="3">
         <v>94</v>
       </c>
@@ -12026,7 +12040,7 @@
       </c>
       <c r="BB83" s="12"/>
     </row>
-    <row r="84" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A84" s="3">
         <v>95</v>
       </c>
@@ -12145,7 +12159,7 @@
       </c>
       <c r="BB84" s="12"/>
     </row>
-    <row r="85" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A85" s="3">
         <v>96</v>
       </c>
@@ -12264,7 +12278,7 @@
       </c>
       <c r="BB85" s="12"/>
     </row>
-    <row r="86" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A86" s="3">
         <v>97</v>
       </c>
@@ -12383,7 +12397,7 @@
       </c>
       <c r="BB86" s="12"/>
     </row>
-    <row r="87" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A87" s="3">
         <v>98</v>
       </c>
@@ -12502,7 +12516,7 @@
       </c>
       <c r="BB87" s="12"/>
     </row>
-    <row r="88" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A88" s="3">
         <v>99</v>
       </c>
@@ -12621,7 +12635,7 @@
       </c>
       <c r="BB88" s="12"/>
     </row>
-    <row r="89" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A89" s="3">
         <v>100</v>
       </c>
@@ -12740,7 +12754,7 @@
       </c>
       <c r="BB89" s="12"/>
     </row>
-    <row r="90" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A90" s="3">
         <v>101</v>
       </c>
@@ -12859,7 +12873,7 @@
       </c>
       <c r="BB90" s="12"/>
     </row>
-    <row r="91" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A91" s="3">
         <v>102</v>
       </c>
@@ -12978,7 +12992,7 @@
       </c>
       <c r="BB91" s="12"/>
     </row>
-    <row r="92" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A92" s="3">
         <v>103</v>
       </c>
@@ -13097,7 +13111,7 @@
       </c>
       <c r="BB92" s="12"/>
     </row>
-    <row r="93" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A93" s="3">
         <v>104</v>
       </c>
@@ -13216,7 +13230,7 @@
       </c>
       <c r="BB93" s="12"/>
     </row>
-    <row r="94" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A94" s="3">
         <v>105</v>
       </c>
@@ -13335,7 +13349,7 @@
       </c>
       <c r="BB94" s="12"/>
     </row>
-    <row r="95" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A95" s="3">
         <v>106</v>
       </c>
@@ -13454,7 +13468,7 @@
       </c>
       <c r="BB95" s="12"/>
     </row>
-    <row r="96" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A96" s="3">
         <v>107</v>
       </c>
@@ -13573,7 +13587,7 @@
       </c>
       <c r="BB96" s="12"/>
     </row>
-    <row r="97" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A97" s="3">
         <v>108</v>
       </c>
@@ -13692,7 +13706,7 @@
       </c>
       <c r="BB97" s="12"/>
     </row>
-    <row r="98" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A98" s="3">
         <v>109</v>
       </c>
@@ -13811,7 +13825,7 @@
       </c>
       <c r="BB98" s="12"/>
     </row>
-    <row r="99" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A99" s="3">
         <v>110</v>
       </c>
@@ -13930,7 +13944,7 @@
       </c>
       <c r="BB99" s="12"/>
     </row>
-    <row r="100" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A100" s="3">
         <v>111</v>
       </c>
@@ -14049,7 +14063,7 @@
       </c>
       <c r="BB100" s="12"/>
     </row>
-    <row r="101" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A101" s="3">
         <v>112</v>
       </c>
@@ -14168,7 +14182,7 @@
       </c>
       <c r="BB101" s="12"/>
     </row>
-    <row r="102" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A102" s="3">
         <v>113</v>
       </c>
@@ -14287,7 +14301,7 @@
       </c>
       <c r="BB102" s="12"/>
     </row>
-    <row r="103" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A103" s="3">
         <v>114</v>
       </c>
@@ -14406,7 +14420,7 @@
       </c>
       <c r="BB103" s="12"/>
     </row>
-    <row r="104" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A104" s="3">
         <v>115</v>
       </c>
@@ -14525,7 +14539,7 @@
       </c>
       <c r="BB104" s="12"/>
     </row>
-    <row r="105" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A105" s="3">
         <v>116</v>
       </c>
@@ -14644,7 +14658,7 @@
       </c>
       <c r="BB105" s="12"/>
     </row>
-    <row r="106" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A106" s="3">
         <v>117</v>
       </c>
@@ -14763,7 +14777,7 @@
       </c>
       <c r="BB106" s="12"/>
     </row>
-    <row r="107" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A107" s="3">
         <v>118</v>
       </c>
@@ -14889,7 +14903,7 @@
       <c r="AQ107" s="11"/>
       <c r="BB107" s="12"/>
     </row>
-    <row r="108" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A108" s="3">
         <v>119</v>
       </c>
@@ -15015,7 +15029,7 @@
       <c r="AQ108" s="11"/>
       <c r="BB108" s="12"/>
     </row>
-    <row r="109" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A109" s="3">
         <v>120</v>
       </c>
@@ -15141,7 +15155,7 @@
       <c r="AQ109" s="11"/>
       <c r="BB109" s="12"/>
     </row>
-    <row r="110" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A110" s="3">
         <v>121</v>
       </c>
@@ -15267,7 +15281,7 @@
       <c r="AQ110" s="11"/>
       <c r="BB110" s="12"/>
     </row>
-    <row r="111" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A111" s="3">
         <v>122</v>
       </c>
@@ -15393,7 +15407,7 @@
       <c r="AQ111" s="11"/>
       <c r="BB111" s="12"/>
     </row>
-    <row r="112" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A112" s="3">
         <v>123</v>
       </c>
@@ -15519,7 +15533,7 @@
       <c r="AQ112" s="11"/>
       <c r="BB112" s="12"/>
     </row>
-    <row r="113" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A113" s="3">
         <v>124</v>
       </c>
@@ -15645,7 +15659,7 @@
       <c r="AQ113" s="11"/>
       <c r="BB113" s="12"/>
     </row>
-    <row r="114" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A114" s="3">
         <v>125</v>
       </c>
@@ -15771,7 +15785,7 @@
       <c r="AQ114" s="11"/>
       <c r="BB114" s="12"/>
     </row>
-    <row r="115" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A115" s="3">
         <v>126</v>
       </c>
@@ -15897,7 +15911,7 @@
       <c r="AQ115" s="11"/>
       <c r="BB115" s="12"/>
     </row>
-    <row r="116" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A116" s="3">
         <v>127</v>
       </c>
@@ -16023,7 +16037,7 @@
       <c r="AQ116" s="11"/>
       <c r="BB116" s="12"/>
     </row>
-    <row r="117" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A117" s="3">
         <v>128</v>
       </c>
@@ -16149,7 +16163,7 @@
       <c r="AQ117" s="11"/>
       <c r="BB117" s="12"/>
     </row>
-    <row r="118" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A118" s="3">
         <v>129</v>
       </c>
@@ -16275,7 +16289,7 @@
       <c r="AQ118" s="11"/>
       <c r="BB118" s="12"/>
     </row>
-    <row r="119" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A119" s="3">
         <v>130</v>
       </c>
@@ -16401,7 +16415,7 @@
       <c r="AQ119" s="11"/>
       <c r="BB119" s="12"/>
     </row>
-    <row r="120" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A120" s="3">
         <v>131</v>
       </c>
@@ -16527,7 +16541,7 @@
       <c r="AQ120" s="11"/>
       <c r="BB120" s="12"/>
     </row>
-    <row r="121" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A121" s="3">
         <v>132</v>
       </c>
@@ -16653,7 +16667,7 @@
       <c r="AQ121" s="11"/>
       <c r="BB121" s="12"/>
     </row>
-    <row r="122" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A122" s="3">
         <v>133</v>
       </c>
@@ -16772,7 +16786,7 @@
       </c>
       <c r="BB122" s="12"/>
     </row>
-    <row r="123" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A123" s="3">
         <v>134</v>
       </c>
@@ -16891,7 +16905,7 @@
       </c>
       <c r="BB123" s="12"/>
     </row>
-    <row r="124" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A124" s="3">
         <v>135</v>
       </c>
@@ -17010,7 +17024,7 @@
       </c>
       <c r="BB124" s="12"/>
     </row>
-    <row r="125" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A125" s="3">
         <v>136</v>
       </c>
@@ -17129,7 +17143,7 @@
       </c>
       <c r="BB125" s="12"/>
     </row>
-    <row r="126" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A126" s="3">
         <v>137</v>
       </c>
@@ -17248,7 +17262,7 @@
       </c>
       <c r="BB126" s="12"/>
     </row>
-    <row r="127" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A127" s="3">
         <v>138</v>
       </c>
@@ -17367,7 +17381,7 @@
       </c>
       <c r="BB127" s="12"/>
     </row>
-    <row r="128" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A128" s="3" t="s">
         <v>10</v>
       </c>
@@ -17486,7 +17500,7 @@
       </c>
       <c r="BB128" s="12"/>
     </row>
-    <row r="129" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A129" s="3">
         <v>139</v>
       </c>
@@ -17605,7 +17619,7 @@
       </c>
       <c r="BB129" s="12"/>
     </row>
-    <row r="130" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A130" s="3">
         <v>140</v>
       </c>
@@ -17724,7 +17738,7 @@
       </c>
       <c r="BB130" s="12"/>
     </row>
-    <row r="131" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A131" s="3">
         <v>141</v>
       </c>
@@ -17843,7 +17857,7 @@
       </c>
       <c r="BB131" s="12"/>
     </row>
-    <row r="132" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A132" s="3">
         <v>142</v>
       </c>
@@ -17962,7 +17976,7 @@
       </c>
       <c r="BB132" s="12"/>
     </row>
-    <row r="133" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A133" s="3">
         <v>143</v>
       </c>
@@ -18081,7 +18095,7 @@
       </c>
       <c r="BB133" s="12"/>
     </row>
-    <row r="134" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A134" s="3">
         <v>144</v>
       </c>
@@ -18200,7 +18214,7 @@
       </c>
       <c r="BB134" s="12"/>
     </row>
-    <row r="135" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A135" s="3">
         <v>146</v>
       </c>
@@ -18319,7 +18333,7 @@
       </c>
       <c r="BB135" s="12"/>
     </row>
-    <row r="136" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A136" s="3">
         <v>147</v>
       </c>
@@ -18438,7 +18452,7 @@
       </c>
       <c r="BB136" s="12"/>
     </row>
-    <row r="137" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A137" s="3">
         <v>148</v>
       </c>
@@ -18557,7 +18571,7 @@
       </c>
       <c r="BB137" s="12"/>
     </row>
-    <row r="138" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A138" s="3">
         <v>149</v>
       </c>
@@ -18676,7 +18690,7 @@
       </c>
       <c r="BB138" s="12"/>
     </row>
-    <row r="139" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A139" s="3">
         <v>150</v>
       </c>
@@ -18795,7 +18809,7 @@
       </c>
       <c r="BB139" s="12"/>
     </row>
-    <row r="140" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A140" s="3">
         <v>151</v>
       </c>
@@ -18914,7 +18928,7 @@
       </c>
       <c r="BB140" s="12"/>
     </row>
-    <row r="141" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A141" s="3">
         <v>152</v>
       </c>
@@ -19033,7 +19047,7 @@
       </c>
       <c r="BB141" s="12"/>
     </row>
-    <row r="142" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A142" s="3">
         <v>153</v>
       </c>
@@ -19152,7 +19166,7 @@
       </c>
       <c r="BB142" s="12"/>
     </row>
-    <row r="143" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A143" s="3">
         <v>154</v>
       </c>
@@ -19271,7 +19285,7 @@
       </c>
       <c r="BB143" s="12"/>
     </row>
-    <row r="144" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A144" s="3">
         <v>155</v>
       </c>
@@ -19390,7 +19404,7 @@
       </c>
       <c r="BB144" s="12"/>
     </row>
-    <row r="145" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A145" s="3">
         <v>156</v>
       </c>
@@ -19509,7 +19523,7 @@
       </c>
       <c r="BB145" s="12"/>
     </row>
-    <row r="146" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A146" s="3">
         <v>157</v>
       </c>
@@ -19628,7 +19642,7 @@
       </c>
       <c r="BB146" s="12"/>
     </row>
-    <row r="147" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A147" s="3">
         <v>158</v>
       </c>
@@ -19747,7 +19761,7 @@
       </c>
       <c r="BB147" s="12"/>
     </row>
-    <row r="148" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A148" s="3">
         <v>159</v>
       </c>
@@ -19866,7 +19880,7 @@
       </c>
       <c r="BB148" s="12"/>
     </row>
-    <row r="149" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A149" s="3">
         <v>160</v>
       </c>
@@ -19985,7 +19999,7 @@
       </c>
       <c r="BB149" s="12"/>
     </row>
-    <row r="150" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A150" s="3">
         <v>161</v>
       </c>
@@ -20104,7 +20118,7 @@
       </c>
       <c r="BB150" s="12"/>
     </row>
-    <row r="151" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A151" s="3">
         <v>162</v>
       </c>
@@ -20223,7 +20237,7 @@
       </c>
       <c r="BB151" s="12"/>
     </row>
-    <row r="152" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:54" x14ac:dyDescent="0.35">
       <c r="G152" s="27"/>
       <c r="H152" s="27"/>
       <c r="J152" s="27"/>
@@ -20236,7 +20250,7 @@
       <c r="U152" s="2"/>
       <c r="BB152" s="12"/>
     </row>
-    <row r="153" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:54" x14ac:dyDescent="0.35">
       <c r="G153" s="27"/>
       <c r="H153" s="27"/>
       <c r="J153" s="27"/>
@@ -20249,7 +20263,7 @@
       <c r="U153" s="2"/>
       <c r="BB153" s="12"/>
     </row>
-    <row r="154" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:54" x14ac:dyDescent="0.35">
       <c r="G154" s="27"/>
       <c r="H154" s="27"/>
       <c r="J154" s="27"/>
@@ -20262,7 +20276,7 @@
       <c r="U154" s="2"/>
       <c r="BB154" s="12"/>
     </row>
-    <row r="155" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:54" x14ac:dyDescent="0.35">
       <c r="G155" s="27"/>
       <c r="H155" s="27"/>
       <c r="J155" s="27"/>
@@ -20275,7 +20289,7 @@
       <c r="U155" s="2"/>
       <c r="BB155" s="12"/>
     </row>
-    <row r="156" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:54" x14ac:dyDescent="0.35">
       <c r="G156" s="27"/>
       <c r="H156" s="27"/>
       <c r="J156" s="27"/>
@@ -20288,7 +20302,7 @@
       <c r="U156" s="2"/>
       <c r="BB156" s="12"/>
     </row>
-    <row r="157" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:54" x14ac:dyDescent="0.35">
       <c r="G157" s="27"/>
       <c r="H157" s="27"/>
       <c r="J157" s="27"/>
@@ -20301,7 +20315,7 @@
       <c r="U157" s="2"/>
       <c r="BB157" s="12"/>
     </row>
-    <row r="158" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:54" x14ac:dyDescent="0.35">
       <c r="G158" s="27"/>
       <c r="H158" s="27"/>
       <c r="J158" s="27"/>
@@ -20314,7 +20328,7 @@
       <c r="U158" s="2"/>
       <c r="BB158" s="12"/>
     </row>
-    <row r="159" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:54" x14ac:dyDescent="0.35">
       <c r="G159" s="27"/>
       <c r="H159" s="27"/>
       <c r="J159" s="27"/>
@@ -20327,7 +20341,7 @@
       <c r="U159" s="2"/>
       <c r="BB159" s="12"/>
     </row>
-    <row r="160" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:54" x14ac:dyDescent="0.35">
       <c r="G160" s="27"/>
       <c r="H160" s="27"/>
       <c r="J160" s="27"/>
@@ -20340,7 +20354,7 @@
       <c r="U160" s="2"/>
       <c r="BB160" s="12"/>
     </row>
-    <row r="161" spans="7:56" x14ac:dyDescent="0.3">
+    <row r="161" spans="7:56" x14ac:dyDescent="0.35">
       <c r="G161" s="27"/>
       <c r="H161" s="27"/>
       <c r="J161" s="27"/>
@@ -20353,7 +20367,7 @@
       <c r="U161" s="2"/>
       <c r="BB161" s="12"/>
     </row>
-    <row r="162" spans="7:56" x14ac:dyDescent="0.3">
+    <row r="162" spans="7:56" x14ac:dyDescent="0.35">
       <c r="G162" s="27"/>
       <c r="H162" s="27"/>
       <c r="J162" s="27"/>
@@ -20366,7 +20380,7 @@
       <c r="U162" s="2"/>
       <c r="BB162" s="12"/>
     </row>
-    <row r="163" spans="7:56" x14ac:dyDescent="0.3">
+    <row r="163" spans="7:56" x14ac:dyDescent="0.35">
       <c r="G163" s="27"/>
       <c r="H163" s="27"/>
       <c r="J163" s="27"/>
@@ -20379,7 +20393,7 @@
       <c r="U163" s="2"/>
       <c r="BB163" s="12"/>
     </row>
-    <row r="164" spans="7:56" x14ac:dyDescent="0.3">
+    <row r="164" spans="7:56" x14ac:dyDescent="0.35">
       <c r="G164" s="27"/>
       <c r="H164" s="27"/>
       <c r="J164" s="27"/>
@@ -20394,7 +20408,7 @@
       <c r="BC164" s="23"/>
       <c r="BD164" s="23"/>
     </row>
-    <row r="165" spans="7:56" x14ac:dyDescent="0.3">
+    <row r="165" spans="7:56" x14ac:dyDescent="0.35">
       <c r="G165" s="27"/>
       <c r="H165" s="27"/>
       <c r="J165" s="27"/>
@@ -20407,7 +20421,7 @@
       <c r="U165" s="2"/>
       <c r="BB165" s="12"/>
     </row>
-    <row r="166" spans="7:56" x14ac:dyDescent="0.3">
+    <row r="166" spans="7:56" x14ac:dyDescent="0.35">
       <c r="G166" s="27"/>
       <c r="H166" s="27"/>
       <c r="J166" s="27"/>
@@ -20420,7 +20434,7 @@
       <c r="U166" s="2"/>
       <c r="BB166" s="12"/>
     </row>
-    <row r="167" spans="7:56" x14ac:dyDescent="0.3">
+    <row r="167" spans="7:56" x14ac:dyDescent="0.35">
       <c r="G167" s="27"/>
       <c r="H167" s="27"/>
       <c r="J167" s="27"/>
@@ -20433,7 +20447,7 @@
       <c r="U167" s="2"/>
       <c r="BB167" s="12"/>
     </row>
-    <row r="168" spans="7:56" x14ac:dyDescent="0.3">
+    <row r="168" spans="7:56" x14ac:dyDescent="0.35">
       <c r="G168" s="27"/>
       <c r="H168" s="27"/>
       <c r="J168" s="27"/>
@@ -20446,7 +20460,7 @@
       <c r="U168" s="2"/>
       <c r="BB168" s="12"/>
     </row>
-    <row r="169" spans="7:56" x14ac:dyDescent="0.3">
+    <row r="169" spans="7:56" x14ac:dyDescent="0.35">
       <c r="G169" s="27"/>
       <c r="H169" s="27"/>
       <c r="J169" s="27"/>
@@ -20459,7 +20473,7 @@
       <c r="U169" s="2"/>
       <c r="BB169" s="12"/>
     </row>
-    <row r="170" spans="7:56" x14ac:dyDescent="0.3">
+    <row r="170" spans="7:56" x14ac:dyDescent="0.35">
       <c r="G170" s="27"/>
       <c r="H170" s="27"/>
       <c r="J170" s="27"/>
@@ -20472,7 +20486,7 @@
       <c r="U170" s="2"/>
       <c r="BB170" s="12"/>
     </row>
-    <row r="171" spans="7:56" x14ac:dyDescent="0.3">
+    <row r="171" spans="7:56" x14ac:dyDescent="0.35">
       <c r="G171" s="27"/>
       <c r="H171" s="27"/>
       <c r="J171" s="27"/>
@@ -20485,7 +20499,7 @@
       <c r="U171" s="2"/>
       <c r="BB171" s="12"/>
     </row>
-    <row r="172" spans="7:56" x14ac:dyDescent="0.3">
+    <row r="172" spans="7:56" x14ac:dyDescent="0.35">
       <c r="G172" s="27"/>
       <c r="H172" s="27"/>
       <c r="J172" s="27"/>
@@ -20498,7 +20512,7 @@
       <c r="U172" s="2"/>
       <c r="BB172" s="12"/>
     </row>
-    <row r="173" spans="7:56" x14ac:dyDescent="0.3">
+    <row r="173" spans="7:56" x14ac:dyDescent="0.35">
       <c r="G173" s="27"/>
       <c r="H173" s="27"/>
       <c r="J173" s="27"/>
@@ -20511,7 +20525,7 @@
       <c r="U173" s="2"/>
       <c r="BB173" s="12"/>
     </row>
-    <row r="174" spans="7:56" x14ac:dyDescent="0.3">
+    <row r="174" spans="7:56" x14ac:dyDescent="0.35">
       <c r="G174" s="27"/>
       <c r="H174" s="27"/>
       <c r="J174" s="27"/>
@@ -20524,7 +20538,7 @@
       <c r="U174" s="2"/>
       <c r="BB174" s="12"/>
     </row>
-    <row r="175" spans="7:56" x14ac:dyDescent="0.3">
+    <row r="175" spans="7:56" x14ac:dyDescent="0.35">
       <c r="G175" s="27"/>
       <c r="H175" s="27"/>
       <c r="J175" s="27"/>
@@ -20537,7 +20551,7 @@
       <c r="U175" s="2"/>
       <c r="BB175" s="12"/>
     </row>
-    <row r="176" spans="7:56" x14ac:dyDescent="0.3">
+    <row r="176" spans="7:56" x14ac:dyDescent="0.35">
       <c r="G176" s="27"/>
       <c r="H176" s="27"/>
       <c r="J176" s="27"/>
@@ -20550,7 +20564,7 @@
       <c r="U176" s="2"/>
       <c r="BB176" s="12"/>
     </row>
-    <row r="177" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="177" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G177" s="27"/>
       <c r="H177" s="27"/>
       <c r="J177" s="27"/>
@@ -20563,7 +20577,7 @@
       <c r="U177" s="2"/>
       <c r="BB177" s="12"/>
     </row>
-    <row r="178" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="178" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G178" s="27"/>
       <c r="H178" s="27"/>
       <c r="J178" s="27"/>
@@ -20576,7 +20590,7 @@
       <c r="U178" s="2"/>
       <c r="BB178" s="12"/>
     </row>
-    <row r="179" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="179" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G179" s="27"/>
       <c r="H179" s="27"/>
       <c r="J179" s="27"/>
@@ -20589,7 +20603,7 @@
       <c r="U179" s="2"/>
       <c r="BB179" s="12"/>
     </row>
-    <row r="180" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="180" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G180" s="27"/>
       <c r="H180" s="27"/>
       <c r="J180" s="27"/>
@@ -20602,7 +20616,7 @@
       <c r="U180" s="2"/>
       <c r="BB180" s="12"/>
     </row>
-    <row r="181" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="181" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G181" s="27"/>
       <c r="H181" s="27"/>
       <c r="J181" s="27"/>
@@ -20615,7 +20629,7 @@
       <c r="U181" s="2"/>
       <c r="BB181" s="12"/>
     </row>
-    <row r="182" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="182" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G182" s="27"/>
       <c r="H182" s="27"/>
       <c r="J182" s="27"/>
@@ -20628,7 +20642,7 @@
       <c r="U182" s="2"/>
       <c r="BB182" s="12"/>
     </row>
-    <row r="183" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="183" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G183" s="27"/>
       <c r="H183" s="27"/>
       <c r="J183" s="27"/>
@@ -20641,7 +20655,7 @@
       <c r="U183" s="2"/>
       <c r="BB183" s="12"/>
     </row>
-    <row r="184" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="184" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G184" s="27"/>
       <c r="H184" s="27"/>
       <c r="J184" s="27"/>
@@ -20654,7 +20668,7 @@
       <c r="U184" s="2"/>
       <c r="BB184" s="12"/>
     </row>
-    <row r="185" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="185" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G185" s="27"/>
       <c r="H185" s="27"/>
       <c r="J185" s="27"/>
@@ -20667,7 +20681,7 @@
       <c r="U185" s="2"/>
       <c r="BB185" s="12"/>
     </row>
-    <row r="186" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="186" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G186" s="27"/>
       <c r="H186" s="27"/>
       <c r="J186" s="27"/>
@@ -20680,7 +20694,7 @@
       <c r="U186" s="2"/>
       <c r="BB186" s="12"/>
     </row>
-    <row r="187" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="187" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G187" s="27"/>
       <c r="H187" s="27"/>
       <c r="J187" s="27"/>
@@ -20693,7 +20707,7 @@
       <c r="U187" s="2"/>
       <c r="BB187" s="12"/>
     </row>
-    <row r="188" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="188" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G188" s="27"/>
       <c r="H188" s="27"/>
       <c r="J188" s="27"/>
@@ -20706,7 +20720,7 @@
       <c r="U188" s="2"/>
       <c r="BB188" s="12"/>
     </row>
-    <row r="189" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="189" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G189" s="27"/>
       <c r="H189" s="27"/>
       <c r="J189" s="27"/>
@@ -20719,7 +20733,7 @@
       <c r="U189" s="2"/>
       <c r="BB189" s="12"/>
     </row>
-    <row r="190" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="190" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G190" s="27"/>
       <c r="H190" s="27"/>
       <c r="J190" s="27"/>
@@ -20732,7 +20746,7 @@
       <c r="U190" s="2"/>
       <c r="BB190" s="12"/>
     </row>
-    <row r="191" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="191" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G191" s="27"/>
       <c r="H191" s="27"/>
       <c r="J191" s="27"/>
@@ -20745,7 +20759,7 @@
       <c r="U191" s="2"/>
       <c r="BB191" s="12"/>
     </row>
-    <row r="192" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="192" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G192" s="27"/>
       <c r="H192" s="27"/>
       <c r="J192" s="27"/>
@@ -20758,7 +20772,7 @@
       <c r="U192" s="2"/>
       <c r="BB192" s="12"/>
     </row>
-    <row r="193" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="193" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G193" s="27"/>
       <c r="H193" s="27"/>
       <c r="J193" s="27"/>
@@ -20771,7 +20785,7 @@
       <c r="U193" s="2"/>
       <c r="BB193" s="12"/>
     </row>
-    <row r="194" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="194" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G194" s="27"/>
       <c r="H194" s="27"/>
       <c r="J194" s="27"/>
@@ -20784,7 +20798,7 @@
       <c r="U194" s="2"/>
       <c r="BB194" s="12"/>
     </row>
-    <row r="195" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="195" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G195" s="27"/>
       <c r="H195" s="27"/>
       <c r="J195" s="27"/>
@@ -20797,7 +20811,7 @@
       <c r="U195" s="2"/>
       <c r="BB195" s="12"/>
     </row>
-    <row r="196" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="196" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G196" s="27"/>
       <c r="H196" s="27"/>
       <c r="J196" s="27"/>
@@ -20810,7 +20824,7 @@
       <c r="U196" s="2"/>
       <c r="BB196" s="12"/>
     </row>
-    <row r="197" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="197" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G197" s="27"/>
       <c r="H197" s="27"/>
       <c r="J197" s="27"/>
@@ -20823,7 +20837,7 @@
       <c r="U197" s="2"/>
       <c r="BB197" s="12"/>
     </row>
-    <row r="198" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="198" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G198" s="27"/>
       <c r="H198" s="27"/>
       <c r="J198" s="27"/>
@@ -20836,7 +20850,7 @@
       <c r="U198" s="2"/>
       <c r="BB198" s="12"/>
     </row>
-    <row r="199" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="199" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G199" s="27"/>
       <c r="H199" s="27"/>
       <c r="J199" s="27"/>
@@ -20849,7 +20863,7 @@
       <c r="U199" s="2"/>
       <c r="BB199" s="12"/>
     </row>
-    <row r="200" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="200" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G200" s="27"/>
       <c r="H200" s="27"/>
       <c r="J200" s="27"/>
@@ -20862,7 +20876,7 @@
       <c r="U200" s="2"/>
       <c r="BB200" s="12"/>
     </row>
-    <row r="201" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="201" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G201" s="27"/>
       <c r="H201" s="27"/>
       <c r="J201" s="27"/>
@@ -20875,7 +20889,7 @@
       <c r="U201" s="2"/>
       <c r="BB201" s="12"/>
     </row>
-    <row r="202" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="202" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G202" s="27"/>
       <c r="H202" s="27"/>
       <c r="J202" s="27"/>
@@ -20888,7 +20902,7 @@
       <c r="U202" s="2"/>
       <c r="BB202" s="12"/>
     </row>
-    <row r="203" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="203" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G203" s="27"/>
       <c r="H203" s="27"/>
       <c r="J203" s="27"/>
@@ -20901,7 +20915,7 @@
       <c r="U203" s="2"/>
       <c r="BB203" s="12"/>
     </row>
-    <row r="204" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="204" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G204" s="27"/>
       <c r="H204" s="27"/>
       <c r="J204" s="27"/>
@@ -20914,7 +20928,7 @@
       <c r="U204" s="2"/>
       <c r="BB204" s="12"/>
     </row>
-    <row r="205" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="205" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G205" s="27"/>
       <c r="H205" s="27"/>
       <c r="J205" s="27"/>
@@ -20927,7 +20941,7 @@
       <c r="U205" s="2"/>
       <c r="BB205" s="12"/>
     </row>
-    <row r="206" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="206" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G206" s="27"/>
       <c r="H206" s="27"/>
       <c r="J206" s="27"/>
@@ -20940,7 +20954,7 @@
       <c r="U206" s="2"/>
       <c r="BB206" s="12"/>
     </row>
-    <row r="207" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="207" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G207" s="27"/>
       <c r="H207" s="27"/>
       <c r="J207" s="27"/>
@@ -20953,7 +20967,7 @@
       <c r="U207" s="2"/>
       <c r="BB207" s="12"/>
     </row>
-    <row r="208" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="208" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G208" s="27"/>
       <c r="H208" s="27"/>
       <c r="J208" s="27"/>
@@ -20966,7 +20980,7 @@
       <c r="U208" s="2"/>
       <c r="BB208" s="12"/>
     </row>
-    <row r="209" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="209" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G209" s="27"/>
       <c r="H209" s="27"/>
       <c r="J209" s="27"/>
@@ -20979,7 +20993,7 @@
       <c r="U209" s="2"/>
       <c r="BB209" s="12"/>
     </row>
-    <row r="210" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="210" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G210" s="27"/>
       <c r="H210" s="27"/>
       <c r="J210" s="27"/>
@@ -20992,7 +21006,7 @@
       <c r="U210" s="2"/>
       <c r="BB210" s="12"/>
     </row>
-    <row r="211" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="211" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G211" s="27"/>
       <c r="H211" s="27"/>
       <c r="J211" s="27"/>
@@ -21005,7 +21019,7 @@
       <c r="U211" s="2"/>
       <c r="BB211" s="12"/>
     </row>
-    <row r="212" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="212" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G212" s="27"/>
       <c r="H212" s="27"/>
       <c r="J212" s="27"/>
@@ -21018,7 +21032,7 @@
       <c r="U212" s="2"/>
       <c r="BB212" s="12"/>
     </row>
-    <row r="213" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="213" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G213" s="27"/>
       <c r="H213" s="27"/>
       <c r="J213" s="27"/>
@@ -21031,7 +21045,7 @@
       <c r="U213" s="2"/>
       <c r="BB213" s="12"/>
     </row>
-    <row r="214" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="214" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G214" s="27"/>
       <c r="H214" s="27"/>
       <c r="J214" s="27"/>
@@ -21044,7 +21058,7 @@
       <c r="U214" s="2"/>
       <c r="BB214" s="12"/>
     </row>
-    <row r="215" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="215" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G215" s="27"/>
       <c r="H215" s="27"/>
       <c r="J215" s="27"/>
@@ -21057,7 +21071,7 @@
       <c r="U215" s="2"/>
       <c r="BB215" s="12"/>
     </row>
-    <row r="216" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="216" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G216" s="27"/>
       <c r="H216" s="27"/>
       <c r="J216" s="27"/>
@@ -21070,7 +21084,7 @@
       <c r="U216" s="2"/>
       <c r="BB216" s="12"/>
     </row>
-    <row r="217" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="217" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G217" s="27"/>
       <c r="H217" s="27"/>
       <c r="J217" s="27"/>
@@ -21083,7 +21097,7 @@
       <c r="U217" s="2"/>
       <c r="BB217" s="12"/>
     </row>
-    <row r="218" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="218" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G218" s="27"/>
       <c r="H218" s="27"/>
       <c r="J218" s="27"/>
@@ -21096,7 +21110,7 @@
       <c r="U218" s="2"/>
       <c r="BB218" s="12"/>
     </row>
-    <row r="219" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="219" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G219" s="27"/>
       <c r="H219" s="27"/>
       <c r="J219" s="27"/>
@@ -21109,7 +21123,7 @@
       <c r="U219" s="2"/>
       <c r="BB219" s="12"/>
     </row>
-    <row r="220" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="220" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G220" s="27"/>
       <c r="H220" s="27"/>
       <c r="J220" s="27"/>
@@ -21122,7 +21136,7 @@
       <c r="U220" s="2"/>
       <c r="BB220" s="12"/>
     </row>
-    <row r="221" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="221" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G221" s="27"/>
       <c r="H221" s="27"/>
       <c r="J221" s="27"/>
@@ -21135,7 +21149,7 @@
       <c r="U221" s="2"/>
       <c r="BB221" s="12"/>
     </row>
-    <row r="222" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="222" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G222" s="27"/>
       <c r="H222" s="27"/>
       <c r="J222" s="27"/>
@@ -21148,7 +21162,7 @@
       <c r="U222" s="2"/>
       <c r="BB222" s="12"/>
     </row>
-    <row r="223" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="223" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G223" s="27"/>
       <c r="H223" s="27"/>
       <c r="J223" s="27"/>
@@ -21161,7 +21175,7 @@
       <c r="U223" s="2"/>
       <c r="BB223" s="12"/>
     </row>
-    <row r="224" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="224" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G224" s="27"/>
       <c r="H224" s="27"/>
       <c r="J224" s="27"/>
@@ -21174,7 +21188,7 @@
       <c r="U224" s="2"/>
       <c r="BB224" s="12"/>
     </row>
-    <row r="225" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="225" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G225" s="27"/>
       <c r="H225" s="27"/>
       <c r="J225" s="27"/>
@@ -21187,7 +21201,7 @@
       <c r="U225" s="2"/>
       <c r="BB225" s="12"/>
     </row>
-    <row r="226" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="226" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G226" s="27"/>
       <c r="H226" s="27"/>
       <c r="J226" s="27"/>
@@ -21200,7 +21214,7 @@
       <c r="U226" s="2"/>
       <c r="BB226" s="12"/>
     </row>
-    <row r="227" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="227" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G227" s="27"/>
       <c r="H227" s="27"/>
       <c r="J227" s="27"/>
@@ -21213,7 +21227,7 @@
       <c r="U227" s="2"/>
       <c r="BB227" s="12"/>
     </row>
-    <row r="228" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="228" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G228" s="27"/>
       <c r="H228" s="27"/>
       <c r="J228" s="27"/>
@@ -21225,7 +21239,7 @@
       <c r="T228" s="27"/>
       <c r="U228" s="2"/>
     </row>
-    <row r="229" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="229" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G229" s="27"/>
       <c r="H229" s="27"/>
       <c r="J229" s="27"/>
@@ -21237,7 +21251,7 @@
       <c r="T229" s="27"/>
       <c r="U229" s="2"/>
     </row>
-    <row r="230" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="230" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G230" s="27"/>
       <c r="H230" s="27"/>
       <c r="J230" s="27"/>
@@ -21249,7 +21263,7 @@
       <c r="T230" s="27"/>
       <c r="U230" s="2"/>
     </row>
-    <row r="231" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="231" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G231" s="27"/>
       <c r="H231" s="27"/>
       <c r="J231" s="27"/>
@@ -21261,7 +21275,7 @@
       <c r="T231" s="27"/>
       <c r="U231" s="2"/>
     </row>
-    <row r="232" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="232" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G232" s="27"/>
       <c r="H232" s="27"/>
       <c r="J232" s="27"/>
@@ -21273,7 +21287,7 @@
       <c r="T232" s="27"/>
       <c r="U232" s="2"/>
     </row>
-    <row r="233" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="233" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G233" s="27"/>
       <c r="H233" s="27"/>
       <c r="J233" s="27"/>
@@ -21285,7 +21299,7 @@
       <c r="T233" s="27"/>
       <c r="U233" s="2"/>
     </row>
-    <row r="234" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="234" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G234" s="27"/>
       <c r="H234" s="27"/>
       <c r="J234" s="27"/>
@@ -21297,7 +21311,7 @@
       <c r="T234" s="27"/>
       <c r="U234" s="2"/>
     </row>
-    <row r="235" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="235" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G235" s="27"/>
       <c r="H235" s="27"/>
       <c r="J235" s="27"/>
@@ -21309,7 +21323,7 @@
       <c r="T235" s="27"/>
       <c r="U235" s="2"/>
     </row>
-    <row r="236" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="236" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G236" s="27"/>
       <c r="H236" s="27"/>
       <c r="J236" s="27"/>
@@ -21321,7 +21335,7 @@
       <c r="T236" s="27"/>
       <c r="U236" s="2"/>
     </row>
-    <row r="237" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="237" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G237" s="27"/>
       <c r="H237" s="27"/>
       <c r="J237" s="27"/>
@@ -21333,7 +21347,7 @@
       <c r="T237" s="27"/>
       <c r="U237" s="2"/>
     </row>
-    <row r="238" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="238" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G238" s="27"/>
       <c r="H238" s="27"/>
       <c r="J238" s="27"/>
@@ -21345,7 +21359,7 @@
       <c r="T238" s="27"/>
       <c r="U238" s="2"/>
     </row>
-    <row r="239" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="239" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G239" s="27"/>
       <c r="H239" s="27"/>
       <c r="J239" s="27"/>
@@ -21357,7 +21371,7 @@
       <c r="T239" s="27"/>
       <c r="U239" s="2"/>
     </row>
-    <row r="240" spans="7:54" x14ac:dyDescent="0.3">
+    <row r="240" spans="7:54" x14ac:dyDescent="0.35">
       <c r="G240" s="27"/>
       <c r="H240" s="27"/>
       <c r="J240" s="27"/>
@@ -21369,7 +21383,7 @@
       <c r="T240" s="27"/>
       <c r="U240" s="2"/>
     </row>
-    <row r="241" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="241" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G241" s="27"/>
       <c r="H241" s="27"/>
       <c r="J241" s="27"/>
@@ -21381,7 +21395,7 @@
       <c r="T241" s="27"/>
       <c r="U241" s="2"/>
     </row>
-    <row r="242" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="242" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G242" s="27"/>
       <c r="H242" s="27"/>
       <c r="J242" s="27"/>
@@ -21393,7 +21407,7 @@
       <c r="T242" s="27"/>
       <c r="U242" s="2"/>
     </row>
-    <row r="243" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="243" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G243" s="27"/>
       <c r="H243" s="27"/>
       <c r="J243" s="27"/>
@@ -21405,7 +21419,7 @@
       <c r="T243" s="27"/>
       <c r="U243" s="2"/>
     </row>
-    <row r="244" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="244" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G244" s="27"/>
       <c r="H244" s="27"/>
       <c r="J244" s="27"/>
@@ -21417,7 +21431,7 @@
       <c r="T244" s="27"/>
       <c r="U244" s="2"/>
     </row>
-    <row r="245" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="245" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G245" s="27"/>
       <c r="H245" s="27"/>
       <c r="J245" s="27"/>
@@ -21429,7 +21443,7 @@
       <c r="T245" s="27"/>
       <c r="U245" s="2"/>
     </row>
-    <row r="246" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="246" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G246" s="27"/>
       <c r="H246" s="27"/>
       <c r="J246" s="27"/>
@@ -21441,7 +21455,7 @@
       <c r="T246" s="27"/>
       <c r="U246" s="2"/>
     </row>
-    <row r="247" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="247" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G247" s="27"/>
       <c r="H247" s="27"/>
       <c r="J247" s="27"/>
@@ -21453,7 +21467,7 @@
       <c r="T247" s="27"/>
       <c r="U247" s="2"/>
     </row>
-    <row r="248" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="248" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G248" s="27"/>
       <c r="H248" s="27"/>
       <c r="J248" s="27"/>
@@ -21465,7 +21479,7 @@
       <c r="T248" s="27"/>
       <c r="U248" s="2"/>
     </row>
-    <row r="249" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="249" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G249" s="27"/>
       <c r="H249" s="27"/>
       <c r="J249" s="27"/>
@@ -21477,7 +21491,7 @@
       <c r="T249" s="27"/>
       <c r="U249" s="2"/>
     </row>
-    <row r="250" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="250" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G250" s="27"/>
       <c r="H250" s="27"/>
       <c r="J250" s="27"/>
@@ -21489,7 +21503,7 @@
       <c r="T250" s="27"/>
       <c r="U250" s="2"/>
     </row>
-    <row r="251" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="251" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G251" s="27"/>
       <c r="H251" s="27"/>
       <c r="J251" s="27"/>
@@ -21501,7 +21515,7 @@
       <c r="T251" s="27"/>
       <c r="U251" s="2"/>
     </row>
-    <row r="252" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="252" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G252" s="27"/>
       <c r="H252" s="27"/>
       <c r="J252" s="27"/>
@@ -21513,7 +21527,7 @@
       <c r="T252" s="27"/>
       <c r="U252" s="2"/>
     </row>
-    <row r="253" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="253" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G253" s="27"/>
       <c r="H253" s="27"/>
       <c r="J253" s="27"/>
@@ -21525,7 +21539,7 @@
       <c r="T253" s="27"/>
       <c r="U253" s="2"/>
     </row>
-    <row r="254" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="254" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G254" s="27"/>
       <c r="H254" s="27"/>
       <c r="J254" s="27"/>
@@ -21537,7 +21551,7 @@
       <c r="T254" s="27"/>
       <c r="U254" s="2"/>
     </row>
-    <row r="255" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="255" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G255" s="27"/>
       <c r="H255" s="27"/>
       <c r="J255" s="27"/>
@@ -21549,7 +21563,7 @@
       <c r="T255" s="27"/>
       <c r="U255" s="2"/>
     </row>
-    <row r="256" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="256" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G256" s="27"/>
       <c r="H256" s="27"/>
       <c r="J256" s="27"/>
@@ -21561,7 +21575,7 @@
       <c r="T256" s="27"/>
       <c r="U256" s="2"/>
     </row>
-    <row r="257" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="257" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G257" s="27"/>
       <c r="H257" s="27"/>
       <c r="J257" s="27"/>
@@ -21573,7 +21587,7 @@
       <c r="T257" s="27"/>
       <c r="U257" s="2"/>
     </row>
-    <row r="258" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="258" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G258" s="27"/>
       <c r="H258" s="27"/>
       <c r="J258" s="27"/>
@@ -21585,7 +21599,7 @@
       <c r="T258" s="27"/>
       <c r="U258" s="2"/>
     </row>
-    <row r="259" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="259" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G259" s="27"/>
       <c r="H259" s="27"/>
       <c r="J259" s="27"/>
@@ -21597,7 +21611,7 @@
       <c r="T259" s="27"/>
       <c r="U259" s="2"/>
     </row>
-    <row r="260" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="260" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G260" s="27"/>
       <c r="H260" s="27"/>
       <c r="J260" s="27"/>
@@ -21609,7 +21623,7 @@
       <c r="T260" s="27"/>
       <c r="U260" s="2"/>
     </row>
-    <row r="261" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="261" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G261" s="27"/>
       <c r="H261" s="27"/>
       <c r="J261" s="27"/>
@@ -21621,7 +21635,7 @@
       <c r="T261" s="27"/>
       <c r="U261" s="2"/>
     </row>
-    <row r="262" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="262" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G262" s="27"/>
       <c r="H262" s="27"/>
       <c r="J262" s="27"/>
@@ -21633,7 +21647,7 @@
       <c r="T262" s="27"/>
       <c r="U262" s="2"/>
     </row>
-    <row r="263" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="263" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G263" s="27"/>
       <c r="H263" s="27"/>
       <c r="J263" s="27"/>
@@ -21645,7 +21659,7 @@
       <c r="T263" s="27"/>
       <c r="U263" s="2"/>
     </row>
-    <row r="264" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="264" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G264" s="27"/>
       <c r="H264" s="27"/>
       <c r="J264" s="27"/>
@@ -21657,7 +21671,7 @@
       <c r="T264" s="27"/>
       <c r="U264" s="2"/>
     </row>
-    <row r="265" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="265" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G265" s="27"/>
       <c r="H265" s="27"/>
       <c r="J265" s="27"/>
@@ -21669,7 +21683,7 @@
       <c r="T265" s="27"/>
       <c r="U265" s="2"/>
     </row>
-    <row r="266" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="266" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G266" s="27"/>
       <c r="H266" s="27"/>
       <c r="J266" s="27"/>
@@ -21681,7 +21695,7 @@
       <c r="T266" s="27"/>
       <c r="U266" s="2"/>
     </row>
-    <row r="267" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="267" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G267" s="27"/>
       <c r="H267" s="27"/>
       <c r="J267" s="27"/>
@@ -21693,7 +21707,7 @@
       <c r="T267" s="27"/>
       <c r="U267" s="2"/>
     </row>
-    <row r="268" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="268" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G268" s="27"/>
       <c r="H268" s="27"/>
       <c r="J268" s="27"/>
@@ -21705,7 +21719,7 @@
       <c r="T268" s="27"/>
       <c r="U268" s="2"/>
     </row>
-    <row r="269" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="269" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G269" s="27"/>
       <c r="H269" s="27"/>
       <c r="J269" s="27"/>
@@ -21717,7 +21731,7 @@
       <c r="T269" s="27"/>
       <c r="U269" s="2"/>
     </row>
-    <row r="270" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="270" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G270" s="27"/>
       <c r="H270" s="27"/>
       <c r="J270" s="27"/>
@@ -21729,7 +21743,7 @@
       <c r="T270" s="27"/>
       <c r="U270" s="2"/>
     </row>
-    <row r="271" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="271" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G271" s="27"/>
       <c r="H271" s="27"/>
       <c r="J271" s="27"/>
@@ -21741,7 +21755,7 @@
       <c r="T271" s="27"/>
       <c r="U271" s="2"/>
     </row>
-    <row r="272" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="272" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G272" s="27"/>
       <c r="H272" s="27"/>
       <c r="J272" s="27"/>
@@ -21753,7 +21767,7 @@
       <c r="T272" s="27"/>
       <c r="U272" s="2"/>
     </row>
-    <row r="273" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="273" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G273" s="27"/>
       <c r="H273" s="27"/>
       <c r="J273" s="27"/>
@@ -21765,7 +21779,7 @@
       <c r="T273" s="27"/>
       <c r="U273" s="2"/>
     </row>
-    <row r="274" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="274" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G274" s="27"/>
       <c r="H274" s="27"/>
       <c r="J274" s="27"/>
@@ -21777,7 +21791,7 @@
       <c r="T274" s="27"/>
       <c r="U274" s="2"/>
     </row>
-    <row r="275" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="275" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G275" s="27"/>
       <c r="H275" s="27"/>
       <c r="J275" s="27"/>
@@ -21789,7 +21803,7 @@
       <c r="T275" s="27"/>
       <c r="U275" s="2"/>
     </row>
-    <row r="276" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="276" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G276" s="27"/>
       <c r="H276" s="27"/>
       <c r="J276" s="27"/>
@@ -21801,7 +21815,7 @@
       <c r="T276" s="27"/>
       <c r="U276" s="2"/>
     </row>
-    <row r="277" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="277" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G277" s="27"/>
       <c r="H277" s="27"/>
       <c r="J277" s="27"/>
@@ -21813,7 +21827,7 @@
       <c r="T277" s="27"/>
       <c r="U277" s="2"/>
     </row>
-    <row r="278" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="278" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G278" s="27"/>
       <c r="H278" s="27"/>
       <c r="J278" s="27"/>
@@ -21825,7 +21839,7 @@
       <c r="T278" s="27"/>
       <c r="U278" s="2"/>
     </row>
-    <row r="279" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="279" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G279" s="27"/>
       <c r="H279" s="27"/>
       <c r="J279" s="27"/>
@@ -21837,7 +21851,7 @@
       <c r="T279" s="27"/>
       <c r="U279" s="2"/>
     </row>
-    <row r="280" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="280" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G280" s="27"/>
       <c r="H280" s="27"/>
       <c r="J280" s="27"/>
@@ -21849,7 +21863,7 @@
       <c r="T280" s="27"/>
       <c r="U280" s="2"/>
     </row>
-    <row r="281" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="281" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G281" s="27"/>
       <c r="H281" s="27"/>
       <c r="J281" s="27"/>
@@ -21861,7 +21875,7 @@
       <c r="T281" s="27"/>
       <c r="U281" s="2"/>
     </row>
-    <row r="282" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="282" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G282" s="27"/>
       <c r="H282" s="27"/>
       <c r="J282" s="27"/>
@@ -21873,7 +21887,7 @@
       <c r="T282" s="27"/>
       <c r="U282" s="2"/>
     </row>
-    <row r="283" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="283" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G283" s="27"/>
       <c r="H283" s="27"/>
       <c r="J283" s="27"/>
@@ -21885,7 +21899,7 @@
       <c r="T283" s="27"/>
       <c r="U283" s="2"/>
     </row>
-    <row r="284" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="284" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G284" s="27"/>
       <c r="H284" s="27"/>
       <c r="J284" s="27"/>
@@ -21897,7 +21911,7 @@
       <c r="T284" s="27"/>
       <c r="U284" s="2"/>
     </row>
-    <row r="285" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="285" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G285" s="27"/>
       <c r="H285" s="27"/>
       <c r="J285" s="27"/>
@@ -21909,7 +21923,7 @@
       <c r="T285" s="27"/>
       <c r="U285" s="2"/>
     </row>
-    <row r="286" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="286" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G286" s="27"/>
       <c r="H286" s="27"/>
       <c r="J286" s="27"/>
@@ -21921,7 +21935,7 @@
       <c r="T286" s="27"/>
       <c r="U286" s="2"/>
     </row>
-    <row r="287" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="287" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G287" s="27"/>
       <c r="H287" s="27"/>
       <c r="J287" s="27"/>
@@ -21933,7 +21947,7 @@
       <c r="T287" s="27"/>
       <c r="U287" s="2"/>
     </row>
-    <row r="288" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="288" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G288" s="27"/>
       <c r="H288" s="27"/>
       <c r="J288" s="27"/>
@@ -21945,7 +21959,7 @@
       <c r="T288" s="27"/>
       <c r="U288" s="2"/>
     </row>
-    <row r="289" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="289" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G289" s="27"/>
       <c r="H289" s="27"/>
       <c r="J289" s="27"/>
@@ -21957,7 +21971,7 @@
       <c r="T289" s="27"/>
       <c r="U289" s="2"/>
     </row>
-    <row r="290" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="290" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G290" s="27"/>
       <c r="H290" s="27"/>
       <c r="J290" s="27"/>
@@ -21969,7 +21983,7 @@
       <c r="T290" s="27"/>
       <c r="U290" s="2"/>
     </row>
-    <row r="291" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="291" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G291" s="27"/>
       <c r="H291" s="27"/>
       <c r="J291" s="27"/>
@@ -21981,7 +21995,7 @@
       <c r="T291" s="27"/>
       <c r="U291" s="2"/>
     </row>
-    <row r="292" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="292" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G292" s="27"/>
       <c r="H292" s="27"/>
       <c r="J292" s="27"/>
@@ -21993,7 +22007,7 @@
       <c r="T292" s="27"/>
       <c r="U292" s="2"/>
     </row>
-    <row r="293" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="293" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G293" s="27"/>
       <c r="H293" s="27"/>
       <c r="J293" s="27"/>
@@ -22005,7 +22019,7 @@
       <c r="T293" s="27"/>
       <c r="U293" s="2"/>
     </row>
-    <row r="294" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="294" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G294" s="27"/>
       <c r="H294" s="27"/>
       <c r="J294" s="27"/>
@@ -22017,7 +22031,7 @@
       <c r="T294" s="27"/>
       <c r="U294" s="2"/>
     </row>
-    <row r="295" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="295" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G295" s="27"/>
       <c r="H295" s="27"/>
       <c r="J295" s="27"/>
@@ -22029,7 +22043,7 @@
       <c r="T295" s="27"/>
       <c r="U295" s="2"/>
     </row>
-    <row r="296" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="296" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G296" s="27"/>
       <c r="H296" s="27"/>
       <c r="J296" s="27"/>
@@ -22041,7 +22055,7 @@
       <c r="T296" s="27"/>
       <c r="U296" s="2"/>
     </row>
-    <row r="297" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="297" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G297" s="27"/>
       <c r="H297" s="27"/>
       <c r="J297" s="27"/>
@@ -22053,7 +22067,7 @@
       <c r="T297" s="27"/>
       <c r="U297" s="2"/>
     </row>
-    <row r="298" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="298" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G298" s="27"/>
       <c r="H298" s="27"/>
       <c r="J298" s="27"/>
@@ -22065,7 +22079,7 @@
       <c r="T298" s="27"/>
       <c r="U298" s="2"/>
     </row>
-    <row r="299" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="299" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G299" s="27"/>
       <c r="H299" s="27"/>
       <c r="J299" s="27"/>
@@ -22077,7 +22091,7 @@
       <c r="T299" s="27"/>
       <c r="U299" s="2"/>
     </row>
-    <row r="300" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="300" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G300" s="27"/>
       <c r="H300" s="27"/>
       <c r="J300" s="27"/>
@@ -22089,7 +22103,7 @@
       <c r="T300" s="27"/>
       <c r="U300" s="2"/>
     </row>
-    <row r="301" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="301" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G301" s="27"/>
       <c r="H301" s="27"/>
       <c r="J301" s="27"/>
@@ -22101,7 +22115,7 @@
       <c r="T301" s="27"/>
       <c r="U301" s="2"/>
     </row>
-    <row r="302" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="302" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G302" s="27"/>
       <c r="H302" s="27"/>
       <c r="J302" s="27"/>
@@ -22113,7 +22127,7 @@
       <c r="T302" s="27"/>
       <c r="U302" s="2"/>
     </row>
-    <row r="303" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="303" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G303" s="27"/>
       <c r="H303" s="27"/>
       <c r="J303" s="27"/>
@@ -22125,7 +22139,7 @@
       <c r="T303" s="27"/>
       <c r="U303" s="2"/>
     </row>
-    <row r="304" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="304" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G304" s="27"/>
       <c r="H304" s="27"/>
       <c r="J304" s="27"/>
@@ -22137,7 +22151,7 @@
       <c r="T304" s="27"/>
       <c r="U304" s="2"/>
     </row>
-    <row r="305" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="305" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G305" s="27"/>
       <c r="H305" s="27"/>
       <c r="J305" s="27"/>
@@ -22149,7 +22163,7 @@
       <c r="T305" s="27"/>
       <c r="U305" s="2"/>
     </row>
-    <row r="306" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="306" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G306" s="27"/>
       <c r="H306" s="27"/>
       <c r="J306" s="27"/>
@@ -22161,7 +22175,7 @@
       <c r="T306" s="27"/>
       <c r="U306" s="2"/>
     </row>
-    <row r="307" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="307" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G307" s="27"/>
       <c r="H307" s="27"/>
       <c r="J307" s="27"/>
@@ -22173,7 +22187,7 @@
       <c r="T307" s="27"/>
       <c r="U307" s="2"/>
     </row>
-    <row r="308" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="308" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G308" s="27"/>
       <c r="H308" s="27"/>
       <c r="J308" s="27"/>
@@ -22185,7 +22199,7 @@
       <c r="T308" s="27"/>
       <c r="U308" s="2"/>
     </row>
-    <row r="309" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="309" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G309" s="27"/>
       <c r="H309" s="27"/>
       <c r="J309" s="27"/>
@@ -22197,7 +22211,7 @@
       <c r="T309" s="27"/>
       <c r="U309" s="2"/>
     </row>
-    <row r="310" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="310" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G310" s="27"/>
       <c r="H310" s="27"/>
       <c r="J310" s="27"/>
@@ -22209,7 +22223,7 @@
       <c r="T310" s="27"/>
       <c r="U310" s="2"/>
     </row>
-    <row r="311" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="311" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G311" s="27"/>
       <c r="H311" s="27"/>
       <c r="J311" s="27"/>
@@ -22221,7 +22235,7 @@
       <c r="T311" s="27"/>
       <c r="U311" s="2"/>
     </row>
-    <row r="312" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="312" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G312" s="27"/>
       <c r="H312" s="27"/>
       <c r="J312" s="27"/>
@@ -22233,7 +22247,7 @@
       <c r="T312" s="27"/>
       <c r="U312" s="2"/>
     </row>
-    <row r="313" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="313" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G313" s="27"/>
       <c r="H313" s="27"/>
       <c r="J313" s="27"/>
@@ -22245,7 +22259,7 @@
       <c r="T313" s="27"/>
       <c r="U313" s="2"/>
     </row>
-    <row r="314" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="314" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G314" s="27"/>
       <c r="H314" s="27"/>
       <c r="J314" s="27"/>
@@ -22257,7 +22271,7 @@
       <c r="T314" s="27"/>
       <c r="U314" s="2"/>
     </row>
-    <row r="315" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="315" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G315" s="27"/>
       <c r="H315" s="27"/>
       <c r="J315" s="27"/>
@@ -22269,7 +22283,7 @@
       <c r="T315" s="27"/>
       <c r="U315" s="2"/>
     </row>
-    <row r="316" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="316" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G316" s="27"/>
       <c r="H316" s="27"/>
       <c r="J316" s="27"/>
@@ -22281,7 +22295,7 @@
       <c r="T316" s="27"/>
       <c r="U316" s="2"/>
     </row>
-    <row r="317" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="317" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G317" s="27"/>
       <c r="H317" s="27"/>
       <c r="J317" s="27"/>
@@ -22293,7 +22307,7 @@
       <c r="T317" s="27"/>
       <c r="U317" s="2"/>
     </row>
-    <row r="318" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="318" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G318" s="27"/>
       <c r="H318" s="27"/>
       <c r="J318" s="27"/>
@@ -22305,7 +22319,7 @@
       <c r="T318" s="27"/>
       <c r="U318" s="2"/>
     </row>
-    <row r="319" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="319" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G319" s="27"/>
       <c r="H319" s="27"/>
       <c r="J319" s="27"/>
@@ -22317,7 +22331,7 @@
       <c r="T319" s="27"/>
       <c r="U319" s="2"/>
     </row>
-    <row r="320" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="320" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G320" s="27"/>
       <c r="H320" s="27"/>
       <c r="J320" s="27"/>
@@ -22329,7 +22343,7 @@
       <c r="T320" s="27"/>
       <c r="U320" s="2"/>
     </row>
-    <row r="321" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="321" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G321" s="27"/>
       <c r="H321" s="27"/>
       <c r="J321" s="27"/>
@@ -22341,7 +22355,7 @@
       <c r="T321" s="27"/>
       <c r="U321" s="2"/>
     </row>
-    <row r="322" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="322" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G322" s="27"/>
       <c r="H322" s="27"/>
       <c r="J322" s="27"/>
@@ -22353,7 +22367,7 @@
       <c r="T322" s="27"/>
       <c r="U322" s="2"/>
     </row>
-    <row r="323" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="323" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G323" s="27"/>
       <c r="H323" s="27"/>
       <c r="J323" s="27"/>
@@ -22365,7 +22379,7 @@
       <c r="T323" s="27"/>
       <c r="U323" s="2"/>
     </row>
-    <row r="324" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="324" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G324" s="27"/>
       <c r="H324" s="27"/>
       <c r="J324" s="27"/>
@@ -22377,7 +22391,7 @@
       <c r="T324" s="27"/>
       <c r="U324" s="2"/>
     </row>
-    <row r="325" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="325" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G325" s="27"/>
       <c r="H325" s="27"/>
       <c r="J325" s="27"/>
@@ -22389,7 +22403,7 @@
       <c r="T325" s="27"/>
       <c r="U325" s="2"/>
     </row>
-    <row r="326" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="326" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G326" s="27"/>
       <c r="H326" s="27"/>
       <c r="J326" s="27"/>
@@ -22401,7 +22415,7 @@
       <c r="T326" s="27"/>
       <c r="U326" s="2"/>
     </row>
-    <row r="327" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="327" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G327" s="27"/>
       <c r="H327" s="27"/>
       <c r="J327" s="27"/>
@@ -22413,7 +22427,7 @@
       <c r="T327" s="27"/>
       <c r="U327" s="2"/>
     </row>
-    <row r="328" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="328" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G328" s="27"/>
       <c r="H328" s="27"/>
       <c r="J328" s="27"/>
@@ -22425,7 +22439,7 @@
       <c r="T328" s="27"/>
       <c r="U328" s="2"/>
     </row>
-    <row r="329" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="329" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G329" s="27"/>
       <c r="H329" s="27"/>
       <c r="J329" s="27"/>
@@ -22437,7 +22451,7 @@
       <c r="T329" s="27"/>
       <c r="U329" s="2"/>
     </row>
-    <row r="330" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="330" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G330" s="27"/>
       <c r="H330" s="27"/>
       <c r="J330" s="27"/>
@@ -22449,7 +22463,7 @@
       <c r="T330" s="27"/>
       <c r="U330" s="2"/>
     </row>
-    <row r="331" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="331" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G331" s="27"/>
       <c r="H331" s="27"/>
       <c r="J331" s="27"/>
@@ -22461,7 +22475,7 @@
       <c r="T331" s="27"/>
       <c r="U331" s="2"/>
     </row>
-    <row r="332" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="332" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G332" s="27"/>
       <c r="H332" s="27"/>
       <c r="J332" s="27"/>
@@ -22473,7 +22487,7 @@
       <c r="T332" s="27"/>
       <c r="U332" s="2"/>
     </row>
-    <row r="333" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="333" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G333" s="27"/>
       <c r="H333" s="27"/>
       <c r="J333" s="27"/>
@@ -22485,7 +22499,7 @@
       <c r="T333" s="27"/>
       <c r="U333" s="2"/>
     </row>
-    <row r="334" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="334" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G334" s="27"/>
       <c r="H334" s="27"/>
       <c r="J334" s="27"/>
@@ -22497,7 +22511,7 @@
       <c r="T334" s="27"/>
       <c r="U334" s="2"/>
     </row>
-    <row r="335" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="335" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G335" s="27"/>
       <c r="H335" s="27"/>
       <c r="J335" s="27"/>
@@ -22509,7 +22523,7 @@
       <c r="T335" s="27"/>
       <c r="U335" s="2"/>
     </row>
-    <row r="336" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="336" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G336" s="27"/>
       <c r="H336" s="27"/>
       <c r="J336" s="27"/>
@@ -22521,7 +22535,7 @@
       <c r="T336" s="27"/>
       <c r="U336" s="2"/>
     </row>
-    <row r="337" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="337" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G337" s="27"/>
       <c r="H337" s="27"/>
       <c r="J337" s="27"/>
@@ -22533,7 +22547,7 @@
       <c r="T337" s="27"/>
       <c r="U337" s="2"/>
     </row>
-    <row r="338" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="338" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G338" s="27"/>
       <c r="H338" s="27"/>
       <c r="J338" s="27"/>
@@ -22545,7 +22559,7 @@
       <c r="T338" s="27"/>
       <c r="U338" s="2"/>
     </row>
-    <row r="339" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="339" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G339" s="27"/>
       <c r="H339" s="27"/>
       <c r="J339" s="27"/>
@@ -22557,7 +22571,7 @@
       <c r="T339" s="27"/>
       <c r="U339" s="2"/>
     </row>
-    <row r="340" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="340" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G340" s="27"/>
       <c r="H340" s="27"/>
       <c r="J340" s="27"/>
@@ -22569,7 +22583,7 @@
       <c r="T340" s="27"/>
       <c r="U340" s="2"/>
     </row>
-    <row r="341" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="341" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G341" s="27"/>
       <c r="H341" s="27"/>
       <c r="J341" s="27"/>
@@ -22581,7 +22595,7 @@
       <c r="T341" s="27"/>
       <c r="U341" s="2"/>
     </row>
-    <row r="342" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="342" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G342" s="27"/>
       <c r="H342" s="27"/>
       <c r="J342" s="27"/>
@@ -22593,7 +22607,7 @@
       <c r="T342" s="27"/>
       <c r="U342" s="2"/>
     </row>
-    <row r="343" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="343" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G343" s="27"/>
       <c r="H343" s="27"/>
       <c r="J343" s="27"/>
@@ -22605,7 +22619,7 @@
       <c r="T343" s="27"/>
       <c r="U343" s="2"/>
     </row>
-    <row r="344" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="344" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G344" s="27"/>
       <c r="H344" s="27"/>
       <c r="J344" s="27"/>
@@ -22617,7 +22631,7 @@
       <c r="T344" s="27"/>
       <c r="U344" s="2"/>
     </row>
-    <row r="345" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="345" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G345" s="27"/>
       <c r="H345" s="27"/>
       <c r="J345" s="27"/>
@@ -22629,7 +22643,7 @@
       <c r="T345" s="27"/>
       <c r="U345" s="2"/>
     </row>
-    <row r="346" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="346" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G346" s="27"/>
       <c r="H346" s="27"/>
       <c r="J346" s="27"/>
@@ -22641,7 +22655,7 @@
       <c r="T346" s="27"/>
       <c r="U346" s="2"/>
     </row>
-    <row r="347" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="347" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G347" s="27"/>
       <c r="H347" s="27"/>
       <c r="J347" s="27"/>
@@ -22653,7 +22667,7 @@
       <c r="T347" s="27"/>
       <c r="U347" s="2"/>
     </row>
-    <row r="348" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="348" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G348" s="27"/>
       <c r="H348" s="27"/>
       <c r="J348" s="27"/>
@@ -22665,7 +22679,7 @@
       <c r="T348" s="27"/>
       <c r="U348" s="2"/>
     </row>
-    <row r="349" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="349" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G349" s="27"/>
       <c r="H349" s="27"/>
       <c r="J349" s="27"/>
@@ -22677,7 +22691,7 @@
       <c r="T349" s="27"/>
       <c r="U349" s="2"/>
     </row>
-    <row r="350" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="350" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G350" s="27"/>
       <c r="H350" s="27"/>
       <c r="J350" s="27"/>
@@ -22689,7 +22703,7 @@
       <c r="T350" s="27"/>
       <c r="U350" s="2"/>
     </row>
-    <row r="351" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="351" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G351" s="27"/>
       <c r="H351" s="27"/>
       <c r="J351" s="27"/>
@@ -22701,7 +22715,7 @@
       <c r="T351" s="27"/>
       <c r="U351" s="2"/>
     </row>
-    <row r="352" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="352" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G352" s="27"/>
       <c r="H352" s="27"/>
       <c r="J352" s="27"/>
@@ -22713,7 +22727,7 @@
       <c r="T352" s="27"/>
       <c r="U352" s="2"/>
     </row>
-    <row r="353" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="353" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G353" s="27"/>
       <c r="H353" s="27"/>
       <c r="J353" s="27"/>
@@ -22725,7 +22739,7 @@
       <c r="T353" s="27"/>
       <c r="U353" s="2"/>
     </row>
-    <row r="354" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="354" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G354" s="27"/>
       <c r="H354" s="27"/>
       <c r="J354" s="27"/>
@@ -22737,7 +22751,7 @@
       <c r="T354" s="27"/>
       <c r="U354" s="2"/>
     </row>
-    <row r="355" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="355" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G355" s="27"/>
       <c r="H355" s="27"/>
       <c r="J355" s="27"/>
@@ -22749,7 +22763,7 @@
       <c r="T355" s="27"/>
       <c r="U355" s="2"/>
     </row>
-    <row r="356" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="356" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G356" s="27"/>
       <c r="H356" s="27"/>
       <c r="J356" s="27"/>
@@ -22761,7 +22775,7 @@
       <c r="T356" s="27"/>
       <c r="U356" s="2"/>
     </row>
-    <row r="357" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="357" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G357" s="27"/>
       <c r="H357" s="27"/>
       <c r="J357" s="27"/>
@@ -22773,7 +22787,7 @@
       <c r="T357" s="27"/>
       <c r="U357" s="2"/>
     </row>
-    <row r="358" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="358" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G358" s="27"/>
       <c r="H358" s="27"/>
       <c r="J358" s="27"/>
@@ -22785,7 +22799,7 @@
       <c r="T358" s="27"/>
       <c r="U358" s="2"/>
     </row>
-    <row r="359" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="359" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G359" s="27"/>
       <c r="H359" s="27"/>
       <c r="J359" s="27"/>
@@ -22797,7 +22811,7 @@
       <c r="T359" s="27"/>
       <c r="U359" s="2"/>
     </row>
-    <row r="360" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="360" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G360" s="27"/>
       <c r="H360" s="27"/>
       <c r="J360" s="27"/>
@@ -22809,7 +22823,7 @@
       <c r="T360" s="27"/>
       <c r="U360" s="2"/>
     </row>
-    <row r="361" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="361" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G361" s="27"/>
       <c r="H361" s="27"/>
       <c r="J361" s="27"/>
@@ -22821,7 +22835,7 @@
       <c r="T361" s="27"/>
       <c r="U361" s="2"/>
     </row>
-    <row r="362" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="362" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G362" s="27"/>
       <c r="H362" s="27"/>
       <c r="J362" s="27"/>
@@ -22833,7 +22847,7 @@
       <c r="T362" s="27"/>
       <c r="U362" s="2"/>
     </row>
-    <row r="363" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="363" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G363" s="27"/>
       <c r="H363" s="27"/>
       <c r="J363" s="27"/>
@@ -22845,7 +22859,7 @@
       <c r="T363" s="27"/>
       <c r="U363" s="2"/>
     </row>
-    <row r="364" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="364" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G364" s="27"/>
       <c r="H364" s="27"/>
       <c r="J364" s="27"/>
@@ -22857,7 +22871,7 @@
       <c r="T364" s="27"/>
       <c r="U364" s="2"/>
     </row>
-    <row r="365" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="365" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G365" s="27"/>
       <c r="H365" s="27"/>
       <c r="J365" s="27"/>
@@ -22869,7 +22883,7 @@
       <c r="T365" s="27"/>
       <c r="U365" s="2"/>
     </row>
-    <row r="366" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="366" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G366" s="27"/>
       <c r="H366" s="27"/>
       <c r="J366" s="27"/>
@@ -22881,7 +22895,7 @@
       <c r="T366" s="27"/>
       <c r="U366" s="2"/>
     </row>
-    <row r="367" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="367" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G367" s="27"/>
       <c r="H367" s="27"/>
       <c r="J367" s="27"/>
@@ -22893,7 +22907,7 @@
       <c r="T367" s="27"/>
       <c r="U367" s="2"/>
     </row>
-    <row r="368" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="368" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G368" s="27"/>
       <c r="H368" s="27"/>
       <c r="J368" s="27"/>
@@ -22905,7 +22919,7 @@
       <c r="T368" s="27"/>
       <c r="U368" s="2"/>
     </row>
-    <row r="369" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="369" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G369" s="27"/>
       <c r="H369" s="27"/>
       <c r="J369" s="27"/>
@@ -22917,7 +22931,7 @@
       <c r="T369" s="27"/>
       <c r="U369" s="2"/>
     </row>
-    <row r="370" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="370" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G370" s="27"/>
       <c r="H370" s="27"/>
       <c r="J370" s="27"/>
@@ -22929,7 +22943,7 @@
       <c r="T370" s="27"/>
       <c r="U370" s="2"/>
     </row>
-    <row r="371" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="371" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G371" s="27"/>
       <c r="H371" s="27"/>
       <c r="J371" s="27"/>
@@ -22941,7 +22955,7 @@
       <c r="T371" s="27"/>
       <c r="U371" s="2"/>
     </row>
-    <row r="372" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="372" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G372" s="27"/>
       <c r="H372" s="27"/>
       <c r="J372" s="27"/>
@@ -22953,7 +22967,7 @@
       <c r="T372" s="27"/>
       <c r="U372" s="2"/>
     </row>
-    <row r="373" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="373" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G373" s="27"/>
       <c r="H373" s="27"/>
       <c r="J373" s="27"/>
@@ -22965,7 +22979,7 @@
       <c r="T373" s="27"/>
       <c r="U373" s="2"/>
     </row>
-    <row r="374" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="374" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G374" s="27"/>
       <c r="H374" s="27"/>
       <c r="J374" s="27"/>
@@ -22977,7 +22991,7 @@
       <c r="T374" s="27"/>
       <c r="U374" s="2"/>
     </row>
-    <row r="375" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="375" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G375" s="27"/>
       <c r="H375" s="27"/>
       <c r="J375" s="27"/>
@@ -22989,7 +23003,7 @@
       <c r="T375" s="27"/>
       <c r="U375" s="2"/>
     </row>
-    <row r="376" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="376" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G376" s="27"/>
       <c r="H376" s="27"/>
       <c r="J376" s="27"/>
@@ -23001,7 +23015,7 @@
       <c r="T376" s="27"/>
       <c r="U376" s="2"/>
     </row>
-    <row r="377" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="377" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G377" s="27"/>
       <c r="H377" s="27"/>
       <c r="J377" s="27"/>
@@ -23013,7 +23027,7 @@
       <c r="T377" s="27"/>
       <c r="U377" s="2"/>
     </row>
-    <row r="378" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="378" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G378" s="27"/>
       <c r="H378" s="27"/>
       <c r="J378" s="27"/>
@@ -23025,7 +23039,7 @@
       <c r="T378" s="27"/>
       <c r="U378" s="2"/>
     </row>
-    <row r="379" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="379" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G379" s="27"/>
       <c r="H379" s="27"/>
       <c r="J379" s="27"/>
@@ -23037,7 +23051,7 @@
       <c r="T379" s="27"/>
       <c r="U379" s="2"/>
     </row>
-    <row r="380" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="380" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G380" s="27"/>
       <c r="H380" s="27"/>
       <c r="J380" s="27"/>
@@ -23049,7 +23063,7 @@
       <c r="T380" s="27"/>
       <c r="U380" s="2"/>
     </row>
-    <row r="381" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="381" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G381" s="27"/>
       <c r="H381" s="27"/>
       <c r="J381" s="27"/>
@@ -23061,7 +23075,7 @@
       <c r="T381" s="27"/>
       <c r="U381" s="2"/>
     </row>
-    <row r="382" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="382" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G382" s="27"/>
       <c r="H382" s="27"/>
       <c r="J382" s="27"/>
@@ -23073,7 +23087,7 @@
       <c r="T382" s="27"/>
       <c r="U382" s="2"/>
     </row>
-    <row r="383" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="383" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G383" s="27"/>
       <c r="H383" s="27"/>
       <c r="J383" s="27"/>
@@ -23085,7 +23099,7 @@
       <c r="T383" s="27"/>
       <c r="U383" s="2"/>
     </row>
-    <row r="384" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="384" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G384" s="27"/>
       <c r="H384" s="27"/>
       <c r="J384" s="27"/>
@@ -23097,7 +23111,7 @@
       <c r="T384" s="27"/>
       <c r="U384" s="2"/>
     </row>
-    <row r="385" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="385" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G385" s="27"/>
       <c r="H385" s="27"/>
       <c r="J385" s="27"/>
@@ -23109,7 +23123,7 @@
       <c r="T385" s="27"/>
       <c r="U385" s="2"/>
     </row>
-    <row r="386" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="386" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G386" s="27"/>
       <c r="H386" s="27"/>
       <c r="J386" s="27"/>
@@ -23121,7 +23135,7 @@
       <c r="T386" s="27"/>
       <c r="U386" s="2"/>
     </row>
-    <row r="387" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="387" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G387" s="27"/>
       <c r="H387" s="27"/>
       <c r="J387" s="27"/>
@@ -23133,7 +23147,7 @@
       <c r="T387" s="27"/>
       <c r="U387" s="2"/>
     </row>
-    <row r="388" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="388" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G388" s="27"/>
       <c r="H388" s="27"/>
       <c r="J388" s="27"/>
@@ -23145,7 +23159,7 @@
       <c r="T388" s="27"/>
       <c r="U388" s="2"/>
     </row>
-    <row r="389" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="389" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G389" s="27"/>
       <c r="H389" s="27"/>
       <c r="J389" s="27"/>
@@ -23157,7 +23171,7 @@
       <c r="T389" s="27"/>
       <c r="U389" s="2"/>
     </row>
-    <row r="390" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="390" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G390" s="27"/>
       <c r="H390" s="27"/>
       <c r="J390" s="27"/>
@@ -23169,7 +23183,7 @@
       <c r="T390" s="27"/>
       <c r="U390" s="2"/>
     </row>
-    <row r="391" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="391" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G391" s="27"/>
       <c r="H391" s="27"/>
       <c r="J391" s="27"/>
@@ -23181,7 +23195,7 @@
       <c r="T391" s="27"/>
       <c r="U391" s="2"/>
     </row>
-    <row r="392" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="392" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G392" s="27"/>
       <c r="H392" s="27"/>
       <c r="J392" s="27"/>
@@ -23193,7 +23207,7 @@
       <c r="T392" s="27"/>
       <c r="U392" s="2"/>
     </row>
-    <row r="393" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="393" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G393" s="27"/>
       <c r="H393" s="27"/>
       <c r="J393" s="27"/>
@@ -23205,7 +23219,7 @@
       <c r="T393" s="27"/>
       <c r="U393" s="2"/>
     </row>
-    <row r="394" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="394" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G394" s="27"/>
       <c r="H394" s="27"/>
       <c r="J394" s="27"/>
@@ -23217,7 +23231,7 @@
       <c r="T394" s="27"/>
       <c r="U394" s="2"/>
     </row>
-    <row r="395" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="395" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G395" s="27"/>
       <c r="H395" s="27"/>
       <c r="J395" s="27"/>
@@ -23229,7 +23243,7 @@
       <c r="T395" s="27"/>
       <c r="U395" s="2"/>
     </row>
-    <row r="396" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="396" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G396" s="27"/>
       <c r="H396" s="27"/>
       <c r="J396" s="27"/>
@@ -23241,7 +23255,7 @@
       <c r="T396" s="27"/>
       <c r="U396" s="2"/>
     </row>
-    <row r="397" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="397" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G397" s="27"/>
       <c r="H397" s="27"/>
       <c r="J397" s="27"/>
@@ -23253,7 +23267,7 @@
       <c r="T397" s="27"/>
       <c r="U397" s="2"/>
     </row>
-    <row r="398" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="398" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G398" s="27"/>
       <c r="H398" s="27"/>
       <c r="J398" s="27"/>
@@ -23265,7 +23279,7 @@
       <c r="T398" s="27"/>
       <c r="U398" s="2"/>
     </row>
-    <row r="399" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="399" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G399" s="27"/>
       <c r="H399" s="27"/>
       <c r="J399" s="27"/>
@@ -23277,7 +23291,7 @@
       <c r="T399" s="27"/>
       <c r="U399" s="2"/>
     </row>
-    <row r="400" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="400" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G400" s="27"/>
       <c r="H400" s="27"/>
       <c r="J400" s="27"/>
@@ -23289,7 +23303,7 @@
       <c r="T400" s="27"/>
       <c r="U400" s="2"/>
     </row>
-    <row r="401" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="401" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G401" s="27"/>
       <c r="H401" s="27"/>
       <c r="J401" s="27"/>
@@ -23301,7 +23315,7 @@
       <c r="T401" s="27"/>
       <c r="U401" s="2"/>
     </row>
-    <row r="402" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="402" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G402" s="27"/>
       <c r="H402" s="27"/>
       <c r="J402" s="27"/>
@@ -23313,7 +23327,7 @@
       <c r="T402" s="27"/>
       <c r="U402" s="2"/>
     </row>
-    <row r="403" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="403" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G403" s="27"/>
       <c r="H403" s="27"/>
       <c r="J403" s="27"/>
@@ -23325,7 +23339,7 @@
       <c r="T403" s="27"/>
       <c r="U403" s="2"/>
     </row>
-    <row r="404" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="404" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G404" s="27"/>
       <c r="H404" s="27"/>
       <c r="J404" s="27"/>
@@ -23337,7 +23351,7 @@
       <c r="T404" s="27"/>
       <c r="U404" s="2"/>
     </row>
-    <row r="405" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="405" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G405" s="27"/>
       <c r="H405" s="27"/>
       <c r="J405" s="27"/>
@@ -23349,7 +23363,7 @@
       <c r="T405" s="27"/>
       <c r="U405" s="2"/>
     </row>
-    <row r="406" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="406" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G406" s="27"/>
       <c r="H406" s="27"/>
       <c r="J406" s="27"/>
@@ -23361,7 +23375,7 @@
       <c r="T406" s="27"/>
       <c r="U406" s="2"/>
     </row>
-    <row r="407" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="407" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G407" s="27"/>
       <c r="H407" s="27"/>
       <c r="J407" s="27"/>
@@ -23373,7 +23387,7 @@
       <c r="T407" s="27"/>
       <c r="U407" s="2"/>
     </row>
-    <row r="408" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="408" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G408" s="27"/>
       <c r="H408" s="27"/>
       <c r="J408" s="27"/>
@@ -23385,7 +23399,7 @@
       <c r="T408" s="27"/>
       <c r="U408" s="2"/>
     </row>
-    <row r="409" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="409" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G409" s="27"/>
       <c r="H409" s="27"/>
       <c r="J409" s="27"/>
@@ -23397,7 +23411,7 @@
       <c r="T409" s="27"/>
       <c r="U409" s="2"/>
     </row>
-    <row r="410" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="410" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G410" s="27"/>
       <c r="H410" s="27"/>
       <c r="J410" s="27"/>
@@ -23409,7 +23423,7 @@
       <c r="T410" s="27"/>
       <c r="U410" s="2"/>
     </row>
-    <row r="411" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="411" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G411" s="27"/>
       <c r="H411" s="27"/>
       <c r="J411" s="27"/>
@@ -23421,7 +23435,7 @@
       <c r="T411" s="27"/>
       <c r="U411" s="2"/>
     </row>
-    <row r="412" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="412" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G412" s="27"/>
       <c r="H412" s="27"/>
       <c r="J412" s="27"/>
@@ -23433,7 +23447,7 @@
       <c r="T412" s="27"/>
       <c r="U412" s="2"/>
     </row>
-    <row r="413" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="413" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G413" s="27"/>
       <c r="H413" s="27"/>
       <c r="J413" s="27"/>
@@ -23445,7 +23459,7 @@
       <c r="T413" s="27"/>
       <c r="U413" s="2"/>
     </row>
-    <row r="414" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="414" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G414" s="27"/>
       <c r="H414" s="27"/>
       <c r="J414" s="27"/>
@@ -23457,7 +23471,7 @@
       <c r="T414" s="27"/>
       <c r="U414" s="2"/>
     </row>
-    <row r="415" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="415" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G415" s="27"/>
       <c r="H415" s="27"/>
       <c r="J415" s="27"/>
@@ -23469,7 +23483,7 @@
       <c r="T415" s="27"/>
       <c r="U415" s="2"/>
     </row>
-    <row r="416" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="416" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G416" s="27"/>
       <c r="H416" s="27"/>
       <c r="J416" s="27"/>
@@ -23481,7 +23495,7 @@
       <c r="T416" s="27"/>
       <c r="U416" s="2"/>
     </row>
-    <row r="417" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="417" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G417" s="27"/>
       <c r="H417" s="27"/>
       <c r="J417" s="27"/>
@@ -23493,7 +23507,7 @@
       <c r="T417" s="27"/>
       <c r="U417" s="2"/>
     </row>
-    <row r="418" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="418" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G418" s="27"/>
       <c r="H418" s="27"/>
       <c r="J418" s="27"/>
@@ -23505,7 +23519,7 @@
       <c r="T418" s="27"/>
       <c r="U418" s="2"/>
     </row>
-    <row r="419" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="419" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G419" s="27"/>
       <c r="H419" s="27"/>
       <c r="J419" s="27"/>
@@ -23517,7 +23531,7 @@
       <c r="T419" s="27"/>
       <c r="U419" s="2"/>
     </row>
-    <row r="420" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="420" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G420" s="27"/>
       <c r="H420" s="27"/>
       <c r="J420" s="27"/>
@@ -23529,7 +23543,7 @@
       <c r="T420" s="27"/>
       <c r="U420" s="2"/>
     </row>
-    <row r="421" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="421" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G421" s="27"/>
       <c r="H421" s="27"/>
       <c r="J421" s="27"/>
@@ -23541,7 +23555,7 @@
       <c r="T421" s="27"/>
       <c r="U421" s="2"/>
     </row>
-    <row r="422" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="422" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G422" s="27"/>
       <c r="H422" s="27"/>
       <c r="J422" s="27"/>
@@ -23553,7 +23567,7 @@
       <c r="T422" s="27"/>
       <c r="U422" s="2"/>
     </row>
-    <row r="423" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="423" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G423" s="27"/>
       <c r="H423" s="27"/>
       <c r="J423" s="27"/>
@@ -23565,7 +23579,7 @@
       <c r="T423" s="27"/>
       <c r="U423" s="2"/>
     </row>
-    <row r="424" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="424" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G424" s="27"/>
       <c r="H424" s="27"/>
       <c r="J424" s="27"/>
@@ -23577,7 +23591,7 @@
       <c r="T424" s="27"/>
       <c r="U424" s="2"/>
     </row>
-    <row r="425" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="425" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G425" s="27"/>
       <c r="H425" s="27"/>
       <c r="J425" s="27"/>
@@ -23589,7 +23603,7 @@
       <c r="T425" s="27"/>
       <c r="U425" s="2"/>
     </row>
-    <row r="426" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="426" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G426" s="27"/>
       <c r="H426" s="27"/>
       <c r="J426" s="27"/>
@@ -23601,7 +23615,7 @@
       <c r="T426" s="27"/>
       <c r="U426" s="2"/>
     </row>
-    <row r="427" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="427" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G427" s="27"/>
       <c r="H427" s="27"/>
       <c r="J427" s="27"/>
@@ -23613,7 +23627,7 @@
       <c r="T427" s="27"/>
       <c r="U427" s="2"/>
     </row>
-    <row r="428" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="428" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G428" s="27"/>
       <c r="H428" s="27"/>
       <c r="J428" s="27"/>
@@ -23625,7 +23639,7 @@
       <c r="T428" s="27"/>
       <c r="U428" s="2"/>
     </row>
-    <row r="429" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="429" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G429" s="27"/>
       <c r="H429" s="27"/>
       <c r="J429" s="27"/>
@@ -23637,7 +23651,7 @@
       <c r="T429" s="27"/>
       <c r="U429" s="2"/>
     </row>
-    <row r="430" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="430" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G430" s="27"/>
       <c r="H430" s="27"/>
       <c r="J430" s="27"/>
@@ -23649,7 +23663,7 @@
       <c r="T430" s="27"/>
       <c r="U430" s="2"/>
     </row>
-    <row r="431" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="431" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G431" s="27"/>
       <c r="H431" s="27"/>
       <c r="J431" s="27"/>
@@ -23661,7 +23675,7 @@
       <c r="T431" s="27"/>
       <c r="U431" s="2"/>
     </row>
-    <row r="432" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="432" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G432" s="27"/>
       <c r="H432" s="27"/>
       <c r="J432" s="27"/>
@@ -23673,7 +23687,7 @@
       <c r="T432" s="27"/>
       <c r="U432" s="2"/>
     </row>
-    <row r="433" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="433" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G433" s="27"/>
       <c r="H433" s="27"/>
       <c r="J433" s="27"/>
@@ -23685,7 +23699,7 @@
       <c r="T433" s="27"/>
       <c r="U433" s="2"/>
     </row>
-    <row r="434" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="434" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G434" s="27"/>
       <c r="H434" s="27"/>
       <c r="J434" s="27"/>
@@ -23697,7 +23711,7 @@
       <c r="T434" s="27"/>
       <c r="U434" s="2"/>
     </row>
-    <row r="435" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="435" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G435" s="27"/>
       <c r="H435" s="27"/>
       <c r="J435" s="27"/>
@@ -23709,7 +23723,7 @@
       <c r="T435" s="27"/>
       <c r="U435" s="2"/>
     </row>
-    <row r="436" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="436" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G436" s="27"/>
       <c r="H436" s="27"/>
       <c r="J436" s="27"/>
@@ -23721,7 +23735,7 @@
       <c r="T436" s="27"/>
       <c r="U436" s="2"/>
     </row>
-    <row r="437" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="437" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G437" s="27"/>
       <c r="H437" s="27"/>
       <c r="J437" s="27"/>
@@ -23733,7 +23747,7 @@
       <c r="T437" s="27"/>
       <c r="U437" s="2"/>
     </row>
-    <row r="438" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="438" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G438" s="27"/>
       <c r="H438" s="27"/>
       <c r="J438" s="27"/>
@@ -23745,7 +23759,7 @@
       <c r="T438" s="27"/>
       <c r="U438" s="2"/>
     </row>
-    <row r="439" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="439" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G439" s="27"/>
       <c r="H439" s="27"/>
       <c r="J439" s="27"/>
@@ -23757,7 +23771,7 @@
       <c r="T439" s="27"/>
       <c r="U439" s="2"/>
     </row>
-    <row r="440" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="440" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G440" s="27"/>
       <c r="H440" s="27"/>
       <c r="J440" s="27"/>
@@ -23769,7 +23783,7 @@
       <c r="T440" s="27"/>
       <c r="U440" s="2"/>
     </row>
-    <row r="441" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="441" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G441" s="27"/>
       <c r="H441" s="27"/>
       <c r="J441" s="27"/>
@@ -23781,7 +23795,7 @@
       <c r="T441" s="27"/>
       <c r="U441" s="2"/>
     </row>
-    <row r="442" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="442" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G442" s="27"/>
       <c r="H442" s="27"/>
       <c r="J442" s="27"/>
@@ -23793,7 +23807,7 @@
       <c r="T442" s="27"/>
       <c r="U442" s="2"/>
     </row>
-    <row r="443" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="443" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G443" s="27"/>
       <c r="H443" s="27"/>
       <c r="J443" s="27"/>
@@ -23805,7 +23819,7 @@
       <c r="T443" s="27"/>
       <c r="U443" s="2"/>
     </row>
-    <row r="444" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="444" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G444" s="27"/>
       <c r="H444" s="27"/>
       <c r="J444" s="27"/>
@@ -23817,7 +23831,7 @@
       <c r="T444" s="27"/>
       <c r="U444" s="2"/>
     </row>
-    <row r="445" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="445" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G445" s="27"/>
       <c r="H445" s="27"/>
       <c r="J445" s="27"/>
@@ -23829,7 +23843,7 @@
       <c r="T445" s="27"/>
       <c r="U445" s="2"/>
     </row>
-    <row r="446" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="446" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G446" s="27"/>
       <c r="H446" s="27"/>
       <c r="J446" s="27"/>
@@ -23841,7 +23855,7 @@
       <c r="T446" s="27"/>
       <c r="U446" s="2"/>
     </row>
-    <row r="447" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="447" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G447" s="27"/>
       <c r="H447" s="27"/>
       <c r="J447" s="27"/>
@@ -23853,7 +23867,7 @@
       <c r="T447" s="27"/>
       <c r="U447" s="2"/>
     </row>
-    <row r="448" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="448" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G448" s="27"/>
       <c r="H448" s="27"/>
       <c r="J448" s="27"/>
@@ -23865,7 +23879,7 @@
       <c r="T448" s="27"/>
       <c r="U448" s="2"/>
     </row>
-    <row r="449" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="449" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G449" s="27"/>
       <c r="H449" s="27"/>
       <c r="J449" s="27"/>
@@ -23877,7 +23891,7 @@
       <c r="T449" s="27"/>
       <c r="U449" s="2"/>
     </row>
-    <row r="450" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="450" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G450" s="27"/>
       <c r="H450" s="27"/>
       <c r="J450" s="27"/>
@@ -23889,7 +23903,7 @@
       <c r="T450" s="27"/>
       <c r="U450" s="2"/>
     </row>
-    <row r="451" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="451" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G451" s="27"/>
       <c r="H451" s="27"/>
       <c r="J451" s="27"/>
@@ -23901,7 +23915,7 @@
       <c r="T451" s="27"/>
       <c r="U451" s="2"/>
     </row>
-    <row r="452" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="452" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G452" s="27"/>
       <c r="H452" s="27"/>
       <c r="J452" s="27"/>
@@ -23913,7 +23927,7 @@
       <c r="T452" s="27"/>
       <c r="U452" s="2"/>
     </row>
-    <row r="453" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="453" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G453" s="27"/>
       <c r="H453" s="27"/>
       <c r="J453" s="27"/>
@@ -23925,7 +23939,7 @@
       <c r="T453" s="27"/>
       <c r="U453" s="2"/>
     </row>
-    <row r="454" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="454" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G454" s="27"/>
       <c r="H454" s="27"/>
       <c r="J454" s="27"/>
@@ -23937,7 +23951,7 @@
       <c r="T454" s="27"/>
       <c r="U454" s="2"/>
     </row>
-    <row r="455" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="455" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G455" s="27"/>
       <c r="H455" s="27"/>
       <c r="J455" s="27"/>
@@ -23949,7 +23963,7 @@
       <c r="T455" s="27"/>
       <c r="U455" s="2"/>
     </row>
-    <row r="456" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="456" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G456" s="27"/>
       <c r="H456" s="27"/>
       <c r="J456" s="27"/>
@@ -23961,7 +23975,7 @@
       <c r="T456" s="27"/>
       <c r="U456" s="2"/>
     </row>
-    <row r="457" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="457" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G457" s="27"/>
       <c r="H457" s="27"/>
       <c r="J457" s="27"/>
@@ -23973,7 +23987,7 @@
       <c r="T457" s="27"/>
       <c r="U457" s="2"/>
     </row>
-    <row r="458" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="458" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G458" s="27"/>
       <c r="H458" s="27"/>
       <c r="J458" s="27"/>
@@ -23985,7 +23999,7 @@
       <c r="T458" s="27"/>
       <c r="U458" s="2"/>
     </row>
-    <row r="459" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="459" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G459" s="27"/>
       <c r="H459" s="27"/>
       <c r="J459" s="27"/>
@@ -23997,7 +24011,7 @@
       <c r="T459" s="27"/>
       <c r="U459" s="2"/>
     </row>
-    <row r="460" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="460" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G460" s="27"/>
       <c r="H460" s="27"/>
       <c r="J460" s="27"/>
@@ -24009,7 +24023,7 @@
       <c r="T460" s="27"/>
       <c r="U460" s="2"/>
     </row>
-    <row r="461" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="461" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G461" s="27"/>
       <c r="H461" s="27"/>
       <c r="J461" s="27"/>
@@ -24021,7 +24035,7 @@
       <c r="T461" s="27"/>
       <c r="U461" s="2"/>
     </row>
-    <row r="462" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="462" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G462" s="27"/>
       <c r="H462" s="27"/>
       <c r="J462" s="27"/>
@@ -24033,7 +24047,7 @@
       <c r="T462" s="27"/>
       <c r="U462" s="2"/>
     </row>
-    <row r="463" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="463" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G463" s="27"/>
       <c r="H463" s="27"/>
       <c r="J463" s="27"/>
@@ -24045,7 +24059,7 @@
       <c r="T463" s="27"/>
       <c r="U463" s="2"/>
     </row>
-    <row r="464" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="464" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G464" s="27"/>
       <c r="H464" s="27"/>
       <c r="J464" s="27"/>
@@ -24057,7 +24071,7 @@
       <c r="T464" s="27"/>
       <c r="U464" s="2"/>
     </row>
-    <row r="465" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="465" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G465" s="27"/>
       <c r="H465" s="27"/>
       <c r="J465" s="27"/>
@@ -24069,7 +24083,7 @@
       <c r="T465" s="27"/>
       <c r="U465" s="2"/>
     </row>
-    <row r="466" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="466" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G466" s="27"/>
       <c r="H466" s="27"/>
       <c r="J466" s="27"/>
@@ -24081,7 +24095,7 @@
       <c r="T466" s="27"/>
       <c r="U466" s="2"/>
     </row>
-    <row r="467" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="467" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G467" s="27"/>
       <c r="H467" s="27"/>
       <c r="J467" s="27"/>
@@ -24093,7 +24107,7 @@
       <c r="T467" s="27"/>
       <c r="U467" s="2"/>
     </row>
-    <row r="468" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="468" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G468" s="27"/>
       <c r="H468" s="27"/>
       <c r="J468" s="27"/>
@@ -24105,7 +24119,7 @@
       <c r="T468" s="27"/>
       <c r="U468" s="2"/>
     </row>
-    <row r="469" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="469" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G469" s="27"/>
       <c r="H469" s="27"/>
       <c r="J469" s="27"/>
@@ -24117,7 +24131,7 @@
       <c r="T469" s="27"/>
       <c r="U469" s="2"/>
     </row>
-    <row r="470" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="470" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G470" s="27"/>
       <c r="H470" s="27"/>
       <c r="J470" s="27"/>
@@ -24129,7 +24143,7 @@
       <c r="T470" s="27"/>
       <c r="U470" s="2"/>
     </row>
-    <row r="471" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="471" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G471" s="27"/>
       <c r="H471" s="27"/>
       <c r="J471" s="27"/>
@@ -24141,7 +24155,7 @@
       <c r="T471" s="27"/>
       <c r="U471" s="2"/>
     </row>
-    <row r="472" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="472" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G472" s="27"/>
       <c r="H472" s="27"/>
       <c r="J472" s="27"/>
@@ -24153,7 +24167,7 @@
       <c r="T472" s="27"/>
       <c r="U472" s="2"/>
     </row>
-    <row r="473" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="473" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G473" s="27"/>
       <c r="H473" s="27"/>
       <c r="J473" s="27"/>
@@ -24165,7 +24179,7 @@
       <c r="T473" s="27"/>
       <c r="U473" s="2"/>
     </row>
-    <row r="474" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="474" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G474" s="27"/>
       <c r="H474" s="27"/>
       <c r="J474" s="27"/>
@@ -24177,7 +24191,7 @@
       <c r="T474" s="27"/>
       <c r="U474" s="2"/>
     </row>
-    <row r="475" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="475" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G475" s="27"/>
       <c r="H475" s="27"/>
       <c r="J475" s="27"/>
@@ -24189,7 +24203,7 @@
       <c r="T475" s="27"/>
       <c r="U475" s="2"/>
     </row>
-    <row r="476" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="476" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G476" s="27"/>
       <c r="H476" s="27"/>
       <c r="J476" s="27"/>
@@ -24201,7 +24215,7 @@
       <c r="T476" s="27"/>
       <c r="U476" s="2"/>
     </row>
-    <row r="477" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="477" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G477" s="27"/>
       <c r="H477" s="27"/>
       <c r="J477" s="27"/>
@@ -24213,7 +24227,7 @@
       <c r="T477" s="27"/>
       <c r="U477" s="2"/>
     </row>
-    <row r="478" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="478" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G478" s="27"/>
       <c r="H478" s="27"/>
       <c r="J478" s="27"/>
@@ -24225,7 +24239,7 @@
       <c r="T478" s="27"/>
       <c r="U478" s="2"/>
     </row>
-    <row r="479" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="479" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G479" s="27"/>
       <c r="H479" s="27"/>
       <c r="J479" s="27"/>
@@ -24237,7 +24251,7 @@
       <c r="T479" s="27"/>
       <c r="U479" s="2"/>
     </row>
-    <row r="480" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="480" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G480" s="27"/>
       <c r="H480" s="27"/>
       <c r="J480" s="27"/>
@@ -24249,7 +24263,7 @@
       <c r="T480" s="27"/>
       <c r="U480" s="2"/>
     </row>
-    <row r="481" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="481" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G481" s="27"/>
       <c r="H481" s="27"/>
       <c r="J481" s="27"/>
@@ -24261,7 +24275,7 @@
       <c r="T481" s="27"/>
       <c r="U481" s="2"/>
     </row>
-    <row r="482" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="482" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G482" s="27"/>
       <c r="H482" s="27"/>
       <c r="J482" s="27"/>
@@ -24273,7 +24287,7 @@
       <c r="T482" s="27"/>
       <c r="U482" s="2"/>
     </row>
-    <row r="483" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="483" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G483" s="27"/>
       <c r="H483" s="27"/>
       <c r="J483" s="27"/>
@@ -24285,7 +24299,7 @@
       <c r="T483" s="27"/>
       <c r="U483" s="2"/>
     </row>
-    <row r="484" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="484" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G484" s="27"/>
       <c r="H484" s="27"/>
       <c r="J484" s="27"/>
@@ -24297,7 +24311,7 @@
       <c r="T484" s="27"/>
       <c r="U484" s="2"/>
     </row>
-    <row r="485" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="485" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G485" s="27"/>
       <c r="H485" s="27"/>
       <c r="J485" s="27"/>
@@ -24309,7 +24323,7 @@
       <c r="T485" s="27"/>
       <c r="U485" s="2"/>
     </row>
-    <row r="486" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="486" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G486" s="27"/>
       <c r="H486" s="27"/>
       <c r="J486" s="27"/>
@@ -24321,7 +24335,7 @@
       <c r="T486" s="27"/>
       <c r="U486" s="2"/>
     </row>
-    <row r="487" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="487" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G487" s="27"/>
       <c r="H487" s="27"/>
       <c r="J487" s="27"/>
@@ -24333,7 +24347,7 @@
       <c r="T487" s="27"/>
       <c r="U487" s="2"/>
     </row>
-    <row r="488" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="488" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G488" s="27"/>
       <c r="H488" s="27"/>
       <c r="J488" s="27"/>
@@ -24345,7 +24359,7 @@
       <c r="T488" s="27"/>
       <c r="U488" s="2"/>
     </row>
-    <row r="489" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="489" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G489" s="27"/>
       <c r="H489" s="27"/>
       <c r="J489" s="27"/>
@@ -24357,7 +24371,7 @@
       <c r="T489" s="27"/>
       <c r="U489" s="2"/>
     </row>
-    <row r="490" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="490" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G490" s="27"/>
       <c r="H490" s="27"/>
       <c r="J490" s="27"/>
@@ -24369,7 +24383,7 @@
       <c r="T490" s="27"/>
       <c r="U490" s="2"/>
     </row>
-    <row r="491" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="491" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G491" s="27"/>
       <c r="H491" s="27"/>
       <c r="J491" s="27"/>
@@ -24381,7 +24395,7 @@
       <c r="T491" s="27"/>
       <c r="U491" s="2"/>
     </row>
-    <row r="492" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="492" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G492" s="27"/>
       <c r="H492" s="27"/>
       <c r="J492" s="27"/>
@@ -24393,7 +24407,7 @@
       <c r="T492" s="27"/>
       <c r="U492" s="2"/>
     </row>
-    <row r="493" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="493" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G493" s="27"/>
       <c r="H493" s="27"/>
       <c r="J493" s="27"/>
@@ -24405,7 +24419,7 @@
       <c r="T493" s="27"/>
       <c r="U493" s="2"/>
     </row>
-    <row r="494" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="494" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G494" s="27"/>
       <c r="H494" s="27"/>
       <c r="J494" s="27"/>
@@ -24417,7 +24431,7 @@
       <c r="T494" s="27"/>
       <c r="U494" s="2"/>
     </row>
-    <row r="495" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="495" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G495" s="27"/>
       <c r="H495" s="27"/>
       <c r="J495" s="27"/>
@@ -24429,7 +24443,7 @@
       <c r="T495" s="27"/>
       <c r="U495" s="2"/>
     </row>
-    <row r="496" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="496" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G496" s="27"/>
       <c r="H496" s="27"/>
       <c r="J496" s="27"/>
@@ -24441,7 +24455,7 @@
       <c r="T496" s="27"/>
       <c r="U496" s="2"/>
     </row>
-    <row r="497" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="497" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G497" s="27"/>
       <c r="H497" s="27"/>
       <c r="J497" s="27"/>
@@ -24453,7 +24467,7 @@
       <c r="T497" s="27"/>
       <c r="U497" s="2"/>
     </row>
-    <row r="498" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="498" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G498" s="27"/>
       <c r="H498" s="27"/>
       <c r="J498" s="27"/>
@@ -24465,7 +24479,7 @@
       <c r="T498" s="27"/>
       <c r="U498" s="2"/>
     </row>
-    <row r="499" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="499" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G499" s="27"/>
       <c r="H499" s="27"/>
       <c r="J499" s="27"/>
@@ -24477,7 +24491,7 @@
       <c r="T499" s="27"/>
       <c r="U499" s="2"/>
     </row>
-    <row r="500" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="500" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G500" s="27"/>
       <c r="H500" s="27"/>
       <c r="J500" s="27"/>
@@ -24489,7 +24503,7 @@
       <c r="T500" s="27"/>
       <c r="U500" s="2"/>
     </row>
-    <row r="501" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="501" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G501" s="27"/>
       <c r="H501" s="27"/>
       <c r="J501" s="27"/>
@@ -24501,7 +24515,7 @@
       <c r="T501" s="27"/>
       <c r="U501" s="2"/>
     </row>
-    <row r="502" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="502" spans="7:21" x14ac:dyDescent="0.35">
       <c r="K502" s="2"/>
       <c r="L502" s="27"/>
       <c r="M502" s="2"/>
@@ -24509,7 +24523,7 @@
       <c r="T502" s="27"/>
       <c r="U502" s="2"/>
     </row>
-    <row r="503" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="503" spans="7:21" x14ac:dyDescent="0.35">
       <c r="K503" s="2"/>
       <c r="L503" s="27"/>
       <c r="M503" s="2"/>
@@ -24517,7 +24531,7 @@
       <c r="T503" s="27"/>
       <c r="U503" s="2"/>
     </row>
-    <row r="504" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="504" spans="7:21" x14ac:dyDescent="0.35">
       <c r="K504" s="2"/>
       <c r="L504" s="27"/>
       <c r="M504" s="2"/>
@@ -24525,7 +24539,7 @@
       <c r="T504" s="27"/>
       <c r="U504" s="2"/>
     </row>
-    <row r="505" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="505" spans="7:21" x14ac:dyDescent="0.35">
       <c r="K505" s="2"/>
       <c r="L505" s="27"/>
       <c r="M505" s="2"/>
@@ -24533,7 +24547,7 @@
       <c r="T505" s="27"/>
       <c r="U505" s="2"/>
     </row>
-    <row r="506" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="506" spans="7:21" x14ac:dyDescent="0.35">
       <c r="K506" s="2"/>
       <c r="L506" s="27"/>
       <c r="M506" s="2"/>
@@ -24541,7 +24555,7 @@
       <c r="T506" s="27"/>
       <c r="U506" s="2"/>
     </row>
-    <row r="507" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="507" spans="7:21" x14ac:dyDescent="0.35">
       <c r="K507" s="2"/>
       <c r="L507" s="27"/>
       <c r="M507" s="2"/>
@@ -24549,7 +24563,7 @@
       <c r="T507" s="27"/>
       <c r="U507" s="2"/>
     </row>
-    <row r="508" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="508" spans="7:21" x14ac:dyDescent="0.35">
       <c r="K508" s="2"/>
       <c r="L508" s="27"/>
       <c r="M508" s="2"/>
@@ -24557,7 +24571,7 @@
       <c r="T508" s="27"/>
       <c r="U508" s="2"/>
     </row>
-    <row r="509" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="509" spans="7:21" x14ac:dyDescent="0.35">
       <c r="K509" s="2"/>
       <c r="L509" s="27"/>
       <c r="M509" s="2"/>
@@ -24565,7 +24579,7 @@
       <c r="T509" s="27"/>
       <c r="U509" s="2"/>
     </row>
-    <row r="510" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="510" spans="7:21" x14ac:dyDescent="0.35">
       <c r="K510" s="2"/>
       <c r="L510" s="27"/>
       <c r="M510" s="2"/>
@@ -24573,7 +24587,7 @@
       <c r="T510" s="27"/>
       <c r="U510" s="2"/>
     </row>
-    <row r="511" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="511" spans="7:21" x14ac:dyDescent="0.35">
       <c r="K511" s="2"/>
       <c r="L511" s="27"/>
       <c r="M511" s="2"/>
@@ -24581,7 +24595,7 @@
       <c r="T511" s="27"/>
       <c r="U511" s="2"/>
     </row>
-    <row r="512" spans="7:21" x14ac:dyDescent="0.3">
+    <row r="512" spans="7:21" x14ac:dyDescent="0.35">
       <c r="K512" s="2"/>
       <c r="L512" s="27"/>
       <c r="M512" s="2"/>
@@ -24589,7 +24603,7 @@
       <c r="T512" s="27"/>
       <c r="U512" s="2"/>
     </row>
-    <row r="513" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="513" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K513" s="2"/>
       <c r="L513" s="27"/>
       <c r="M513" s="2"/>
@@ -24597,7 +24611,7 @@
       <c r="T513" s="27"/>
       <c r="U513" s="2"/>
     </row>
-    <row r="514" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="514" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K514" s="2"/>
       <c r="L514" s="27"/>
       <c r="M514" s="2"/>
@@ -24605,7 +24619,7 @@
       <c r="T514" s="27"/>
       <c r="U514" s="2"/>
     </row>
-    <row r="515" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="515" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K515" s="2"/>
       <c r="L515" s="27"/>
       <c r="M515" s="2"/>
@@ -24613,7 +24627,7 @@
       <c r="T515" s="27"/>
       <c r="U515" s="2"/>
     </row>
-    <row r="516" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="516" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K516" s="2"/>
       <c r="L516" s="27"/>
       <c r="M516" s="2"/>
@@ -24621,7 +24635,7 @@
       <c r="T516" s="27"/>
       <c r="U516" s="2"/>
     </row>
-    <row r="517" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="517" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K517" s="2"/>
       <c r="L517" s="27"/>
       <c r="M517" s="2"/>
@@ -24629,7 +24643,7 @@
       <c r="T517" s="27"/>
       <c r="U517" s="2"/>
     </row>
-    <row r="518" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="518" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K518" s="2"/>
       <c r="L518" s="27"/>
       <c r="M518" s="2"/>
@@ -24637,7 +24651,7 @@
       <c r="T518" s="27"/>
       <c r="U518" s="2"/>
     </row>
-    <row r="519" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="519" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K519" s="2"/>
       <c r="L519" s="27"/>
       <c r="M519" s="2"/>
@@ -24645,7 +24659,7 @@
       <c r="T519" s="27"/>
       <c r="U519" s="2"/>
     </row>
-    <row r="520" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="520" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K520" s="2"/>
       <c r="L520" s="27"/>
       <c r="M520" s="2"/>
@@ -24653,7 +24667,7 @@
       <c r="T520" s="27"/>
       <c r="U520" s="2"/>
     </row>
-    <row r="521" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="521" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K521" s="2"/>
       <c r="L521" s="27"/>
       <c r="M521" s="2"/>
@@ -24661,7 +24675,7 @@
       <c r="T521" s="27"/>
       <c r="U521" s="2"/>
     </row>
-    <row r="522" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="522" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K522" s="2"/>
       <c r="L522" s="27"/>
       <c r="M522" s="2"/>
@@ -24669,7 +24683,7 @@
       <c r="T522" s="27"/>
       <c r="U522" s="2"/>
     </row>
-    <row r="523" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="523" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K523" s="2"/>
       <c r="L523" s="27"/>
       <c r="M523" s="2"/>
@@ -24677,7 +24691,7 @@
       <c r="T523" s="27"/>
       <c r="U523" s="2"/>
     </row>
-    <row r="524" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="524" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K524" s="2"/>
       <c r="L524" s="27"/>
       <c r="M524" s="2"/>
@@ -24685,7 +24699,7 @@
       <c r="T524" s="27"/>
       <c r="U524" s="2"/>
     </row>
-    <row r="525" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="525" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K525" s="2"/>
       <c r="L525" s="27"/>
       <c r="M525" s="2"/>
@@ -24693,7 +24707,7 @@
       <c r="T525" s="27"/>
       <c r="U525" s="2"/>
     </row>
-    <row r="526" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="526" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K526" s="2"/>
       <c r="L526" s="27"/>
       <c r="M526" s="2"/>
@@ -24701,7 +24715,7 @@
       <c r="T526" s="27"/>
       <c r="U526" s="2"/>
     </row>
-    <row r="527" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="527" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K527" s="2"/>
       <c r="L527" s="27"/>
       <c r="M527" s="2"/>
@@ -24709,7 +24723,7 @@
       <c r="T527" s="27"/>
       <c r="U527" s="2"/>
     </row>
-    <row r="528" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="528" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K528" s="2"/>
       <c r="L528" s="27"/>
       <c r="M528" s="2"/>
@@ -24717,7 +24731,7 @@
       <c r="T528" s="27"/>
       <c r="U528" s="2"/>
     </row>
-    <row r="529" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="529" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K529" s="2"/>
       <c r="L529" s="27"/>
       <c r="M529" s="2"/>
@@ -24725,7 +24739,7 @@
       <c r="T529" s="27"/>
       <c r="U529" s="2"/>
     </row>
-    <row r="530" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="530" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K530" s="2"/>
       <c r="L530" s="27"/>
       <c r="M530" s="2"/>
@@ -24733,7 +24747,7 @@
       <c r="T530" s="27"/>
       <c r="U530" s="2"/>
     </row>
-    <row r="531" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="531" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K531" s="2"/>
       <c r="L531" s="27"/>
       <c r="M531" s="2"/>
@@ -24741,7 +24755,7 @@
       <c r="T531" s="27"/>
       <c r="U531" s="2"/>
     </row>
-    <row r="532" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="532" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K532" s="2"/>
       <c r="L532" s="27"/>
       <c r="M532" s="2"/>
@@ -24749,7 +24763,7 @@
       <c r="T532" s="27"/>
       <c r="U532" s="2"/>
     </row>
-    <row r="533" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="533" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K533" s="2"/>
       <c r="L533" s="27"/>
       <c r="M533" s="2"/>
@@ -24757,7 +24771,7 @@
       <c r="T533" s="27"/>
       <c r="U533" s="2"/>
     </row>
-    <row r="534" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="534" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K534" s="2"/>
       <c r="L534" s="27"/>
       <c r="M534" s="2"/>
@@ -24765,7 +24779,7 @@
       <c r="T534" s="27"/>
       <c r="U534" s="2"/>
     </row>
-    <row r="535" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="535" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K535" s="2"/>
       <c r="L535" s="27"/>
       <c r="M535" s="2"/>
@@ -24773,7 +24787,7 @@
       <c r="T535" s="27"/>
       <c r="U535" s="2"/>
     </row>
-    <row r="536" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="536" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K536" s="2"/>
       <c r="L536" s="27"/>
       <c r="M536" s="2"/>
@@ -24781,7 +24795,7 @@
       <c r="T536" s="27"/>
       <c r="U536" s="2"/>
     </row>
-    <row r="537" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="537" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K537" s="2"/>
       <c r="L537" s="27"/>
       <c r="M537" s="2"/>
@@ -24789,7 +24803,7 @@
       <c r="T537" s="27"/>
       <c r="U537" s="2"/>
     </row>
-    <row r="538" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="538" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K538" s="2"/>
       <c r="L538" s="27"/>
       <c r="M538" s="2"/>
@@ -24797,7 +24811,7 @@
       <c r="T538" s="27"/>
       <c r="U538" s="2"/>
     </row>
-    <row r="539" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="539" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K539" s="2"/>
       <c r="L539" s="27"/>
       <c r="M539" s="2"/>
@@ -24805,7 +24819,7 @@
       <c r="T539" s="27"/>
       <c r="U539" s="2"/>
     </row>
-    <row r="540" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="540" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K540" s="2"/>
       <c r="L540" s="27"/>
       <c r="M540" s="2"/>
@@ -24813,7 +24827,7 @@
       <c r="T540" s="27"/>
       <c r="U540" s="2"/>
     </row>
-    <row r="541" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="541" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K541" s="2"/>
       <c r="L541" s="27"/>
       <c r="M541" s="2"/>
@@ -24821,7 +24835,7 @@
       <c r="T541" s="27"/>
       <c r="U541" s="2"/>
     </row>
-    <row r="542" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="542" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K542" s="2"/>
       <c r="L542" s="27"/>
       <c r="M542" s="2"/>
@@ -24829,7 +24843,7 @@
       <c r="T542" s="27"/>
       <c r="U542" s="2"/>
     </row>
-    <row r="543" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="543" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K543" s="2"/>
       <c r="L543" s="27"/>
       <c r="M543" s="2"/>
@@ -24837,7 +24851,7 @@
       <c r="T543" s="27"/>
       <c r="U543" s="2"/>
     </row>
-    <row r="544" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="544" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K544" s="2"/>
       <c r="L544" s="27"/>
       <c r="M544" s="2"/>
@@ -24845,7 +24859,7 @@
       <c r="T544" s="27"/>
       <c r="U544" s="2"/>
     </row>
-    <row r="545" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="545" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K545" s="2"/>
       <c r="L545" s="27"/>
       <c r="M545" s="2"/>
@@ -24853,7 +24867,7 @@
       <c r="T545" s="27"/>
       <c r="U545" s="2"/>
     </row>
-    <row r="546" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="546" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K546" s="2"/>
       <c r="L546" s="27"/>
       <c r="M546" s="2"/>
@@ -24861,7 +24875,7 @@
       <c r="T546" s="27"/>
       <c r="U546" s="2"/>
     </row>
-    <row r="547" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="547" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K547" s="2"/>
       <c r="L547" s="27"/>
       <c r="M547" s="2"/>
@@ -24869,7 +24883,7 @@
       <c r="T547" s="27"/>
       <c r="U547" s="2"/>
     </row>
-    <row r="548" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="548" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K548" s="2"/>
       <c r="L548" s="27"/>
       <c r="M548" s="2"/>
@@ -24877,7 +24891,7 @@
       <c r="T548" s="27"/>
       <c r="U548" s="2"/>
     </row>
-    <row r="549" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="549" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K549" s="2"/>
       <c r="L549" s="27"/>
       <c r="M549" s="2"/>
@@ -24885,7 +24899,7 @@
       <c r="T549" s="27"/>
       <c r="U549" s="2"/>
     </row>
-    <row r="550" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="550" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K550" s="2"/>
       <c r="L550" s="27"/>
       <c r="M550" s="2"/>
@@ -24893,7 +24907,7 @@
       <c r="T550" s="27"/>
       <c r="U550" s="2"/>
     </row>
-    <row r="551" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="551" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K551" s="2"/>
       <c r="L551" s="27"/>
       <c r="M551" s="2"/>
@@ -24901,7 +24915,7 @@
       <c r="T551" s="27"/>
       <c r="U551" s="2"/>
     </row>
-    <row r="552" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="552" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K552" s="2"/>
       <c r="L552" s="27"/>
       <c r="M552" s="2"/>
@@ -24909,7 +24923,7 @@
       <c r="T552" s="27"/>
       <c r="U552" s="2"/>
     </row>
-    <row r="553" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="553" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K553" s="2"/>
       <c r="L553" s="27"/>
       <c r="M553" s="2"/>
@@ -24917,7 +24931,7 @@
       <c r="T553" s="27"/>
       <c r="U553" s="2"/>
     </row>
-    <row r="554" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="554" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K554" s="2"/>
       <c r="L554" s="27"/>
       <c r="M554" s="2"/>
@@ -24925,7 +24939,7 @@
       <c r="T554" s="27"/>
       <c r="U554" s="2"/>
     </row>
-    <row r="555" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="555" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K555" s="2"/>
       <c r="L555" s="27"/>
       <c r="M555" s="2"/>
@@ -24933,7 +24947,7 @@
       <c r="T555" s="27"/>
       <c r="U555" s="2"/>
     </row>
-    <row r="556" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="556" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K556" s="2"/>
       <c r="L556" s="27"/>
       <c r="M556" s="2"/>
@@ -24941,7 +24955,7 @@
       <c r="T556" s="27"/>
       <c r="U556" s="2"/>
     </row>
-    <row r="557" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="557" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K557" s="2"/>
       <c r="L557" s="27"/>
       <c r="M557" s="2"/>
@@ -24949,7 +24963,7 @@
       <c r="T557" s="27"/>
       <c r="U557" s="2"/>
     </row>
-    <row r="558" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="558" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K558" s="2"/>
       <c r="L558" s="27"/>
       <c r="M558" s="2"/>
@@ -24957,7 +24971,7 @@
       <c r="T558" s="27"/>
       <c r="U558" s="2"/>
     </row>
-    <row r="559" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="559" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K559" s="2"/>
       <c r="L559" s="27"/>
       <c r="M559" s="2"/>
@@ -24965,7 +24979,7 @@
       <c r="T559" s="27"/>
       <c r="U559" s="2"/>
     </row>
-    <row r="560" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="560" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K560" s="2"/>
       <c r="L560" s="27"/>
       <c r="M560" s="2"/>
@@ -24973,7 +24987,7 @@
       <c r="T560" s="27"/>
       <c r="U560" s="2"/>
     </row>
-    <row r="561" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="561" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K561" s="2"/>
       <c r="L561" s="27"/>
       <c r="M561" s="2"/>
@@ -24981,7 +24995,7 @@
       <c r="T561" s="27"/>
       <c r="U561" s="2"/>
     </row>
-    <row r="562" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="562" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K562" s="2"/>
       <c r="L562" s="27"/>
       <c r="M562" s="2"/>
@@ -24989,7 +25003,7 @@
       <c r="T562" s="27"/>
       <c r="U562" s="2"/>
     </row>
-    <row r="563" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="563" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K563" s="2"/>
       <c r="L563" s="27"/>
       <c r="M563" s="2"/>
@@ -24997,7 +25011,7 @@
       <c r="T563" s="27"/>
       <c r="U563" s="2"/>
     </row>
-    <row r="564" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="564" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K564" s="2"/>
       <c r="L564" s="27"/>
       <c r="M564" s="2"/>
@@ -25005,7 +25019,7 @@
       <c r="T564" s="27"/>
       <c r="U564" s="2"/>
     </row>
-    <row r="565" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="565" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K565" s="2"/>
       <c r="L565" s="27"/>
       <c r="M565" s="2"/>
@@ -25013,7 +25027,7 @@
       <c r="T565" s="27"/>
       <c r="U565" s="2"/>
     </row>
-    <row r="566" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="566" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K566" s="2"/>
       <c r="L566" s="27"/>
       <c r="M566" s="2"/>
@@ -25021,7 +25035,7 @@
       <c r="T566" s="27"/>
       <c r="U566" s="2"/>
     </row>
-    <row r="567" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="567" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K567" s="2"/>
       <c r="L567" s="27"/>
       <c r="M567" s="2"/>
@@ -25029,7 +25043,7 @@
       <c r="T567" s="27"/>
       <c r="U567" s="2"/>
     </row>
-    <row r="568" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="568" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K568" s="2"/>
       <c r="L568" s="27"/>
       <c r="M568" s="2"/>
@@ -25037,7 +25051,7 @@
       <c r="T568" s="27"/>
       <c r="U568" s="2"/>
     </row>
-    <row r="569" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="569" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K569" s="2"/>
       <c r="L569" s="27"/>
       <c r="M569" s="2"/>
@@ -25045,7 +25059,7 @@
       <c r="T569" s="27"/>
       <c r="U569" s="2"/>
     </row>
-    <row r="570" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="570" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K570" s="2"/>
       <c r="L570" s="27"/>
       <c r="M570" s="2"/>
@@ -25053,7 +25067,7 @@
       <c r="T570" s="27"/>
       <c r="U570" s="2"/>
     </row>
-    <row r="571" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="571" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K571" s="2"/>
       <c r="L571" s="27"/>
       <c r="M571" s="2"/>
@@ -25061,7 +25075,7 @@
       <c r="T571" s="27"/>
       <c r="U571" s="2"/>
     </row>
-    <row r="572" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="572" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K572" s="2"/>
       <c r="L572" s="27"/>
       <c r="M572" s="2"/>
@@ -25069,7 +25083,7 @@
       <c r="T572" s="27"/>
       <c r="U572" s="2"/>
     </row>
-    <row r="573" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="573" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K573" s="2"/>
       <c r="L573" s="27"/>
       <c r="M573" s="2"/>
@@ -25077,7 +25091,7 @@
       <c r="T573" s="27"/>
       <c r="U573" s="2"/>
     </row>
-    <row r="574" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="574" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K574" s="2"/>
       <c r="L574" s="27"/>
       <c r="M574" s="2"/>
@@ -25085,7 +25099,7 @@
       <c r="T574" s="27"/>
       <c r="U574" s="2"/>
     </row>
-    <row r="575" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="575" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K575" s="2"/>
       <c r="L575" s="27"/>
       <c r="M575" s="2"/>
@@ -25093,7 +25107,7 @@
       <c r="T575" s="27"/>
       <c r="U575" s="2"/>
     </row>
-    <row r="576" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="576" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K576" s="2"/>
       <c r="L576" s="27"/>
       <c r="M576" s="2"/>
@@ -25101,7 +25115,7 @@
       <c r="T576" s="27"/>
       <c r="U576" s="2"/>
     </row>
-    <row r="577" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="577" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K577" s="2"/>
       <c r="L577" s="27"/>
       <c r="M577" s="2"/>
@@ -25109,7 +25123,7 @@
       <c r="T577" s="27"/>
       <c r="U577" s="2"/>
     </row>
-    <row r="578" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="578" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K578" s="2"/>
       <c r="L578" s="27"/>
       <c r="M578" s="2"/>
@@ -25117,7 +25131,7 @@
       <c r="T578" s="27"/>
       <c r="U578" s="2"/>
     </row>
-    <row r="579" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="579" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K579" s="2"/>
       <c r="L579" s="27"/>
       <c r="M579" s="2"/>
@@ -25125,7 +25139,7 @@
       <c r="T579" s="27"/>
       <c r="U579" s="2"/>
     </row>
-    <row r="580" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="580" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K580" s="2"/>
       <c r="L580" s="27"/>
       <c r="M580" s="2"/>
@@ -25133,7 +25147,7 @@
       <c r="T580" s="27"/>
       <c r="U580" s="2"/>
     </row>
-    <row r="581" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="581" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K581" s="2"/>
       <c r="L581" s="27"/>
       <c r="M581" s="2"/>
@@ -25141,7 +25155,7 @@
       <c r="T581" s="27"/>
       <c r="U581" s="2"/>
     </row>
-    <row r="582" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="582" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K582" s="2"/>
       <c r="L582" s="27"/>
       <c r="M582" s="2"/>
@@ -25149,7 +25163,7 @@
       <c r="T582" s="27"/>
       <c r="U582" s="2"/>
     </row>
-    <row r="583" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="583" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K583" s="2"/>
       <c r="L583" s="27"/>
       <c r="M583" s="2"/>
@@ -25157,7 +25171,7 @@
       <c r="T583" s="27"/>
       <c r="U583" s="2"/>
     </row>
-    <row r="584" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="584" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K584" s="2"/>
       <c r="L584" s="27"/>
       <c r="M584" s="2"/>
@@ -25165,7 +25179,7 @@
       <c r="T584" s="27"/>
       <c r="U584" s="2"/>
     </row>
-    <row r="585" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="585" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K585" s="2"/>
       <c r="L585" s="27"/>
       <c r="M585" s="2"/>
@@ -25173,7 +25187,7 @@
       <c r="T585" s="27"/>
       <c r="U585" s="2"/>
     </row>
-    <row r="586" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="586" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K586" s="2"/>
       <c r="L586" s="27"/>
       <c r="M586" s="2"/>
@@ -25181,7 +25195,7 @@
       <c r="T586" s="27"/>
       <c r="U586" s="2"/>
     </row>
-    <row r="587" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="587" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K587" s="2"/>
       <c r="L587" s="27"/>
       <c r="M587" s="2"/>
@@ -25189,7 +25203,7 @@
       <c r="T587" s="27"/>
       <c r="U587" s="2"/>
     </row>
-    <row r="588" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="588" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K588" s="2"/>
       <c r="L588" s="27"/>
       <c r="M588" s="2"/>
@@ -25197,7 +25211,7 @@
       <c r="T588" s="27"/>
       <c r="U588" s="2"/>
     </row>
-    <row r="589" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="589" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K589" s="2"/>
       <c r="L589" s="27"/>
       <c r="M589" s="2"/>
@@ -25205,7 +25219,7 @@
       <c r="T589" s="27"/>
       <c r="U589" s="2"/>
     </row>
-    <row r="590" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="590" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K590" s="2"/>
       <c r="L590" s="27"/>
       <c r="M590" s="2"/>
@@ -25213,7 +25227,7 @@
       <c r="T590" s="27"/>
       <c r="U590" s="2"/>
     </row>
-    <row r="591" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="591" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K591" s="2"/>
       <c r="L591" s="27"/>
       <c r="M591" s="2"/>
@@ -25221,7 +25235,7 @@
       <c r="T591" s="27"/>
       <c r="U591" s="2"/>
     </row>
-    <row r="592" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="592" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K592" s="2"/>
       <c r="L592" s="27"/>
       <c r="M592" s="2"/>
@@ -25229,7 +25243,7 @@
       <c r="T592" s="27"/>
       <c r="U592" s="2"/>
     </row>
-    <row r="593" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="593" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K593" s="2"/>
       <c r="L593" s="27"/>
       <c r="M593" s="2"/>
@@ -25237,7 +25251,7 @@
       <c r="T593" s="27"/>
       <c r="U593" s="2"/>
     </row>
-    <row r="594" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="594" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K594" s="2"/>
       <c r="L594" s="27"/>
       <c r="M594" s="2"/>
@@ -25245,7 +25259,7 @@
       <c r="T594" s="27"/>
       <c r="U594" s="2"/>
     </row>
-    <row r="595" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="595" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K595" s="2"/>
       <c r="L595" s="27"/>
       <c r="M595" s="2"/>
@@ -25253,7 +25267,7 @@
       <c r="T595" s="27"/>
       <c r="U595" s="2"/>
     </row>
-    <row r="596" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="596" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K596" s="2"/>
       <c r="L596" s="27"/>
       <c r="M596" s="2"/>
@@ -25261,7 +25275,7 @@
       <c r="T596" s="27"/>
       <c r="U596" s="2"/>
     </row>
-    <row r="597" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="597" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K597" s="2"/>
       <c r="L597" s="27"/>
       <c r="M597" s="2"/>
@@ -25269,7 +25283,7 @@
       <c r="T597" s="27"/>
       <c r="U597" s="2"/>
     </row>
-    <row r="598" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="598" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K598" s="2"/>
       <c r="L598" s="27"/>
       <c r="M598" s="2"/>
@@ -25277,7 +25291,7 @@
       <c r="T598" s="27"/>
       <c r="U598" s="2"/>
     </row>
-    <row r="599" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="599" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K599" s="2"/>
       <c r="L599" s="27"/>
       <c r="M599" s="2"/>
@@ -25285,7 +25299,7 @@
       <c r="T599" s="27"/>
       <c r="U599" s="2"/>
     </row>
-    <row r="600" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="600" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K600" s="2"/>
       <c r="L600" s="27"/>
       <c r="M600" s="2"/>
@@ -25293,7 +25307,7 @@
       <c r="T600" s="27"/>
       <c r="U600" s="2"/>
     </row>
-    <row r="601" spans="11:21" x14ac:dyDescent="0.3">
+    <row r="601" spans="11:21" x14ac:dyDescent="0.35">
       <c r="K601" s="2"/>
       <c r="L601" s="27"/>
       <c r="M601" s="2"/>
@@ -25312,12 +25326,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C3C90F0-9117-4AAA-860C-789D5DE6819D}">
   <dimension ref="A1:M151"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>42</v>
       </c>
@@ -25333,7 +25347,7 @@
       <c r="E1" t="s">
         <v>44</v>
       </c>
-      <c r="F1" s="40" t="s">
+      <c r="F1" t="s">
         <v>45</v>
       </c>
       <c r="G1" t="s">
@@ -25358,7 +25372,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -25399,7 +25413,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -25440,7 +25454,7 @@
         <v>13.26</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -25481,7 +25495,7 @@
         <v>14.7</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -25522,7 +25536,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -25563,7 +25577,7 @@
         <v>14.3</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -25604,7 +25618,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -25645,7 +25659,7 @@
         <v>13.65</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -25686,7 +25700,7 @@
         <v>9.9</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -25727,7 +25741,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -25768,7 +25782,7 @@
         <v>13.92</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -25809,7 +25823,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -25850,7 +25864,7 @@
         <v>13.3</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -25891,7 +25905,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -25932,7 +25946,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -25973,7 +25987,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>19</v>
       </c>
@@ -26014,7 +26028,7 @@
         <v>15.2</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>20</v>
       </c>
@@ -26055,7 +26069,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>21</v>
       </c>
@@ -26096,7 +26110,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>22</v>
       </c>
@@ -26137,7 +26151,7 @@
         <v>13.3</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>23</v>
       </c>
@@ -26178,7 +26192,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>24</v>
       </c>
@@ -26219,7 +26233,7 @@
         <v>11.1</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>25</v>
       </c>
@@ -26260,7 +26274,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>26</v>
       </c>
@@ -26301,7 +26315,7 @@
         <v>15.1</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>27</v>
       </c>
@@ -26342,7 +26356,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>28</v>
       </c>
@@ -26383,7 +26397,7 @@
         <v>13.7</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>29</v>
       </c>
@@ -26424,7 +26438,7 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>30</v>
       </c>
@@ -26465,7 +26479,7 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>31</v>
       </c>
@@ -26506,7 +26520,7 @@
         <v>13.3</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>32</v>
       </c>
@@ -26547,7 +26561,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>33</v>
       </c>
@@ -26588,7 +26602,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>37</v>
       </c>
@@ -26629,7 +26643,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>38</v>
       </c>
@@ -26670,7 +26684,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>39</v>
       </c>
@@ -26711,7 +26725,7 @@
         <v>14.8</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>40</v>
       </c>
@@ -26752,7 +26766,7 @@
         <v>13.6</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>41</v>
       </c>
@@ -26793,7 +26807,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>42</v>
       </c>
@@ -26834,7 +26848,7 @@
         <v>13.7</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>43</v>
       </c>
@@ -26875,7 +26889,7 @@
         <v>13.7</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>44</v>
       </c>
@@ -26916,7 +26930,7 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>45</v>
       </c>
@@ -26957,7 +26971,7 @@
         <v>14.3</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>46</v>
       </c>
@@ -26998,7 +27012,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>47</v>
       </c>
@@ -27039,7 +27053,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>48</v>
       </c>
@@ -27080,7 +27094,7 @@
         <v>13.6</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>49</v>
       </c>
@@ -27121,7 +27135,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>50</v>
       </c>
@@ -27162,7 +27176,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>51</v>
       </c>
@@ -27203,7 +27217,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>55</v>
       </c>
@@ -27244,7 +27258,7 @@
         <v>13.44</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>56</v>
       </c>
@@ -27285,7 +27299,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>57</v>
       </c>
@@ -27326,7 +27340,7 @@
         <v>12.18</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>58</v>
       </c>
@@ -27367,7 +27381,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>59</v>
       </c>
@@ -27408,7 +27422,7 @@
         <v>15.4</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>60</v>
       </c>
@@ -27449,7 +27463,7 @@
         <v>13.3</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>61</v>
       </c>
@@ -27490,7 +27504,7 @@
         <v>14.1</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>62</v>
       </c>
@@ -27531,7 +27545,7 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>63</v>
       </c>
@@ -27572,7 +27586,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>64</v>
       </c>
@@ -27613,7 +27627,7 @@
         <v>14.7</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>65</v>
       </c>
@@ -27654,7 +27668,7 @@
         <v>14.35</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>66</v>
       </c>
@@ -27695,7 +27709,7 @@
         <v>13.3</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>67</v>
       </c>
@@ -27736,7 +27750,7 @@
         <v>14.14</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>68</v>
       </c>
@@ -27777,7 +27791,7 @@
         <v>13.1</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>69</v>
       </c>
@@ -27818,7 +27832,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>73</v>
       </c>
@@ -27859,7 +27873,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>74</v>
       </c>
@@ -27900,7 +27914,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>75</v>
       </c>
@@ -27941,7 +27955,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>76</v>
       </c>
@@ -27982,7 +27996,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>77</v>
       </c>
@@ -28023,7 +28037,7 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>78</v>
       </c>
@@ -28064,7 +28078,7 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>79</v>
       </c>
@@ -28105,7 +28119,7 @@
         <v>15.7</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>80</v>
       </c>
@@ -28146,7 +28160,7 @@
         <v>14.9</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>81</v>
       </c>
@@ -28187,7 +28201,7 @@
         <v>14.1</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>82</v>
       </c>
@@ -28228,7 +28242,7 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>83</v>
       </c>
@@ -28269,7 +28283,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>84</v>
       </c>
@@ -28310,7 +28324,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>85</v>
       </c>
@@ -28351,7 +28365,7 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>86</v>
       </c>
@@ -28392,7 +28406,7 @@
         <v>13.9</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>87</v>
       </c>
@@ -28433,7 +28447,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>88</v>
       </c>
@@ -28474,7 +28488,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>89</v>
       </c>
@@ -28515,7 +28529,7 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>90</v>
       </c>
@@ -28556,7 +28570,7 @@
         <v>13.1</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>91</v>
       </c>
@@ -28597,7 +28611,7 @@
         <v>14.8</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>92</v>
       </c>
@@ -28638,7 +28652,7 @@
         <v>14.7</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>93</v>
       </c>
@@ -28679,7 +28693,7 @@
         <v>11.2</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>94</v>
       </c>
@@ -28720,7 +28734,7 @@
         <v>15.3</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>95</v>
       </c>
@@ -28761,7 +28775,7 @@
         <v>13.9</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>96</v>
       </c>
@@ -28802,7 +28816,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>97</v>
       </c>
@@ -28843,7 +28857,7 @@
         <v>12.82</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>98</v>
       </c>
@@ -28884,7 +28898,7 @@
         <v>13.7</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>99</v>
       </c>
@@ -28925,7 +28939,7 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>100</v>
       </c>
@@ -28966,7 +28980,7 @@
         <v>14.3</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>101</v>
       </c>
@@ -29007,7 +29021,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>102</v>
       </c>
@@ -29048,7 +29062,7 @@
         <v>13.6</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>103</v>
       </c>
@@ -29089,7 +29103,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>104</v>
       </c>
@@ -29130,7 +29144,7 @@
         <v>13.1</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>105</v>
       </c>
@@ -29171,7 +29185,7 @@
         <v>15.1</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>106</v>
       </c>
@@ -29212,7 +29226,7 @@
         <v>14.6</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>107</v>
       </c>
@@ -29253,7 +29267,7 @@
         <v>14.9</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>108</v>
       </c>
@@ -29294,7 +29308,7 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>109</v>
       </c>
@@ -29335,7 +29349,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>110</v>
       </c>
@@ -29376,7 +29390,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>111</v>
       </c>
@@ -29417,7 +29431,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>112</v>
       </c>
@@ -29458,7 +29472,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>113</v>
       </c>
@@ -29499,7 +29513,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>114</v>
       </c>
@@ -29540,7 +29554,7 @@
         <v>14.3</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>115</v>
       </c>
@@ -29581,7 +29595,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>116</v>
       </c>
@@ -29622,7 +29636,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>117</v>
       </c>
@@ -29663,7 +29677,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>118</v>
       </c>
@@ -29704,7 +29718,7 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>119</v>
       </c>
@@ -29745,7 +29759,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>120</v>
       </c>
@@ -29786,7 +29800,7 @@
         <v>15.3</v>
       </c>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>121</v>
       </c>
@@ -29827,7 +29841,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>122</v>
       </c>
@@ -29868,7 +29882,7 @@
         <v>13.9</v>
       </c>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>123</v>
       </c>
@@ -29909,7 +29923,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>124</v>
       </c>
@@ -29950,7 +29964,7 @@
         <v>15.9</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>125</v>
       </c>
@@ -29991,7 +30005,7 @@
         <v>14.3</v>
       </c>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>126</v>
       </c>
@@ -30032,7 +30046,7 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>127</v>
       </c>
@@ -30073,7 +30087,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>128</v>
       </c>
@@ -30114,7 +30128,7 @@
         <v>13.6</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>129</v>
       </c>
@@ -30155,7 +30169,7 @@
         <v>15.3</v>
       </c>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>130</v>
       </c>
@@ -30196,7 +30210,7 @@
         <v>13.7</v>
       </c>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>131</v>
       </c>
@@ -30237,7 +30251,7 @@
         <v>13.6</v>
       </c>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>132</v>
       </c>
@@ -30278,7 +30292,7 @@
         <v>14.7</v>
       </c>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>133</v>
       </c>
@@ -30319,7 +30333,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A123">
         <v>134</v>
       </c>
@@ -30360,7 +30374,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>135</v>
       </c>
@@ -30401,7 +30415,7 @@
         <v>13.1</v>
       </c>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>136</v>
       </c>
@@ -30442,7 +30456,7 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A126">
         <v>137</v>
       </c>
@@ -30483,7 +30497,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A127">
         <v>138</v>
       </c>
@@ -30524,7 +30538,7 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A128" s="1" t="s">
         <v>10</v>
       </c>
@@ -30565,7 +30579,7 @@
         <v>14.3</v>
       </c>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A129">
         <v>139</v>
       </c>
@@ -30606,7 +30620,7 @@
         <v>13.36</v>
       </c>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A130">
         <v>140</v>
       </c>
@@ -30647,7 +30661,7 @@
         <v>13.6</v>
       </c>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A131">
         <v>141</v>
       </c>
@@ -30688,7 +30702,7 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A132">
         <v>142</v>
       </c>
@@ -30729,7 +30743,7 @@
         <v>14.36</v>
       </c>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A133">
         <v>143</v>
       </c>
@@ -30770,7 +30784,7 @@
         <v>11.2</v>
       </c>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A134">
         <v>144</v>
       </c>
@@ -30811,7 +30825,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A135">
         <v>146</v>
       </c>
@@ -30852,7 +30866,7 @@
         <v>14.1</v>
       </c>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A136">
         <v>147</v>
       </c>
@@ -30893,7 +30907,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A137">
         <v>148</v>
       </c>
@@ -30934,7 +30948,7 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A138">
         <v>149</v>
       </c>
@@ -30975,7 +30989,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A139">
         <v>150</v>
       </c>
@@ -31016,7 +31030,7 @@
         <v>13.6</v>
       </c>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A140">
         <v>151</v>
       </c>
@@ -31057,7 +31071,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A141">
         <v>152</v>
       </c>
@@ -31098,7 +31112,7 @@
         <v>14.3</v>
       </c>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A142">
         <v>153</v>
       </c>
@@ -31115,7 +31129,7 @@
         <v>66.959879999999998</v>
       </c>
       <c r="F142" s="39">
-        <v>30.073</v>
+        <v>6.19</v>
       </c>
       <c r="G142" s="39">
         <v>26.32</v>
@@ -31139,7 +31153,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A143">
         <v>154</v>
       </c>
@@ -31180,7 +31194,7 @@
         <v>14.1</v>
       </c>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A144">
         <v>155</v>
       </c>
@@ -31221,7 +31235,7 @@
         <v>14.3</v>
       </c>
     </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A145">
         <v>156</v>
       </c>
@@ -31262,7 +31276,7 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A146">
         <v>157</v>
       </c>
@@ -31303,7 +31317,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A147">
         <v>158</v>
       </c>
@@ -31344,7 +31358,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A148">
         <v>159</v>
       </c>
@@ -31385,7 +31399,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A149">
         <v>160</v>
       </c>
@@ -31426,7 +31440,7 @@
         <v>14.8</v>
       </c>
     </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A150">
         <v>161</v>
       </c>
@@ -31467,7 +31481,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A151">
         <v>162</v>
       </c>
